--- a/Lab 02/graph/RunningTimeRecording.xlsx
+++ b/Lab 02/graph/RunningTimeRecording.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\Lab 02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\Lab 02\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2B7E4B-5F13-459E-B29C-C59843D0B664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AWS" sheetId="2" r:id="rId1"/>
@@ -248,17 +248,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -556,38 +556,38 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="17" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="19"/>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="16"/>
+      <c r="H2" s="18"/>
       <c r="I2" s="19"/>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
       <c r="M2" s="19"/>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
     </row>
     <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="18"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
@@ -2225,40 +2225,40 @@
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C37" s="16"/>
+      <c r="C37" s="18"/>
       <c r="D37" s="19"/>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="F37" s="16"/>
+      <c r="F37" s="18"/>
       <c r="G37" s="19"/>
-      <c r="H37" s="15" t="s">
+      <c r="H37" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
       <c r="K37" s="19"/>
-      <c r="L37" s="15" t="s">
+      <c r="L37" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
       <c r="O37" s="19"/>
-      <c r="P37" s="15" t="s">
+      <c r="P37" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="Q37" s="16"/>
-      <c r="R37" s="16"/>
-      <c r="S37" s="16"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="18"/>
+      <c r="S37" s="18"/>
     </row>
     <row r="38" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="18"/>
+      <c r="A38" s="16"/>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
@@ -2543,38 +2543,38 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="17" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="19"/>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="16"/>
+      <c r="H2" s="18"/>
       <c r="I2" s="19"/>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
       <c r="M2" s="19"/>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
     </row>
     <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="18"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
@@ -4398,40 +4398,40 @@
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C37" s="16"/>
+      <c r="C37" s="18"/>
       <c r="D37" s="19"/>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="F37" s="16"/>
+      <c r="F37" s="18"/>
       <c r="G37" s="19"/>
-      <c r="H37" s="15" t="s">
+      <c r="H37" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
       <c r="K37" s="19"/>
-      <c r="L37" s="15" t="s">
+      <c r="L37" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
       <c r="O37" s="19"/>
-      <c r="P37" s="15" t="s">
+      <c r="P37" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="Q37" s="16"/>
-      <c r="R37" s="16"/>
-      <c r="S37" s="16"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="18"/>
+      <c r="S37" s="18"/>
     </row>
     <row r="38" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="18"/>
+      <c r="A38" s="16"/>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>

--- a/Lab 02/graph/RunningTimeRecording.xlsx
+++ b/Lab 02/graph/RunningTimeRecording.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\Lab 02\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2B7E4B-5F13-459E-B29C-C59843D0B664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F967F572-3A52-4FCB-B369-3DAD546E02AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AWS" sheetId="2" r:id="rId1"/>
     <sheet name="CAAS" sheetId="3" r:id="rId2"/>
-    <sheet name="CAAS Graphs" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="30">
   <si>
     <t>N</t>
   </si>
@@ -108,6 +107,27 @@
   <si>
     <t>Open MPI Cyclic (Processes = 16)</t>
   </si>
+  <si>
+    <t>Hybrid Block-Cyclic (Ttl Workers)</t>
+  </si>
+  <si>
+    <t>Hybrid Block-Cyclic (Processes = 4)</t>
+  </si>
+  <si>
+    <t>Hybrid Cyclic (Processes = 4)</t>
+  </si>
+  <si>
+    <t>Workers</t>
+  </si>
+  <si>
+    <t>Processes</t>
+  </si>
+  <si>
+    <t>Threads</t>
+  </si>
+  <si>
+    <t>Hybrid Cyclic (Ttl Workers)</t>
+  </si>
 </sst>
 </file>
 
@@ -130,7 +150,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,6 +160,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -216,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -248,12 +274,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -261,6 +283,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -556,7 +588,7 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="17" t="s">
@@ -587,7 +619,7 @@
       <c r="Q2" s="18"/>
     </row>
     <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="16"/>
+      <c r="A3" s="21"/>
       <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
@@ -2225,7 +2257,7 @@
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="20" t="s">
         <v>11</v>
       </c>
       <c r="B37" s="17" t="s">
@@ -2258,7 +2290,7 @@
       <c r="S37" s="18"/>
     </row>
     <row r="38" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="16"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
@@ -2530,20 +2562,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E341B7-DEDD-4D36-AFDE-6D75EC429377}">
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:AM46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" customWidth="1"/>
-    <col min="2" max="19" width="12.6328125" customWidth="1"/>
+    <col min="2" max="39" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="17" t="s">
@@ -2569,12 +2601,13 @@
       <c r="N2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-    </row>
-    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="16"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="22"/>
+    </row>
+    <row r="3" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21"/>
       <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
@@ -2624,15 +2657,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>10000000</v>
       </c>
       <c r="B4">
-        <v>1.749414</v>
+        <v>1.748899</v>
       </c>
       <c r="C4" s="7">
-        <v>1.812927</v>
+        <v>1.833523</v>
       </c>
       <c r="D4">
         <v>0.218082</v>
@@ -2642,7 +2675,7 @@
       </c>
       <c r="F4" s="9">
         <f>C4/E4</f>
-        <v>6.3706250702799956</v>
+        <v>6.4429994096480376</v>
       </c>
       <c r="G4">
         <v>0.13054199999999999</v>
@@ -2652,44 +2685,44 @@
       </c>
       <c r="I4" s="9">
         <f>C4/H4</f>
-        <v>9.1760784730552558</v>
+        <v>9.2803245415572118</v>
       </c>
       <c r="J4">
-        <v>0.12914800000000001</v>
+        <v>0.15099199999999999</v>
       </c>
       <c r="K4">
-        <v>0.182311</v>
+        <v>0.115922</v>
       </c>
       <c r="L4">
-        <v>0.37195499999999998</v>
+        <v>0.339115</v>
       </c>
       <c r="M4" s="9">
         <f>C4/L4</f>
-        <v>4.8740492801548578</v>
+        <v>5.4067882576707014</v>
       </c>
       <c r="N4">
-        <v>0.151335</v>
+        <v>0.13047700000000001</v>
       </c>
       <c r="O4">
-        <v>0.12816900000000001</v>
+        <v>0.103162</v>
       </c>
       <c r="P4">
-        <v>0.323602</v>
+        <v>0.30353999999999998</v>
       </c>
       <c r="Q4" s="11">
-        <f>C4/P4</f>
-        <v>5.6023355850705494</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" ref="Q4:Q34" si="0">C4/P4</f>
+        <v>6.0404658364630697</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>11000000</v>
       </c>
       <c r="B5">
-        <v>1.998909</v>
+        <v>2.000051</v>
       </c>
       <c r="C5" s="4">
-        <v>2.0694159999999999</v>
+        <v>2.1030500000000001</v>
       </c>
       <c r="D5">
         <v>0.27098800000000001</v>
@@ -2698,8 +2731,8 @@
         <v>0.34778799999999999</v>
       </c>
       <c r="F5" s="9">
-        <f t="shared" ref="F5:F34" si="0">C5/E5</f>
-        <v>5.9502225493691556</v>
+        <f t="shared" ref="F5:F34" si="1">C5/E5</f>
+        <v>6.046930888932339</v>
       </c>
       <c r="G5">
         <v>0.14468500000000001</v>
@@ -2708,45 +2741,45 @@
         <v>0.21735499999999999</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" ref="I5:I34" si="1">C5/H5</f>
-        <v>9.52090359089968</v>
+        <f t="shared" ref="I5:I34" si="2">C5/H5</f>
+        <v>9.6756458328540873</v>
       </c>
       <c r="J5">
-        <v>0.14860699999999999</v>
+        <v>0.15848000000000001</v>
       </c>
       <c r="K5">
-        <v>0.133164</v>
+        <v>0.109898</v>
       </c>
       <c r="L5">
-        <v>0.35451700000000003</v>
+        <v>0.35133300000000001</v>
       </c>
       <c r="M5" s="9">
-        <f t="shared" ref="M5:M34" si="2">C5/L5</f>
-        <v>5.8372828383406148</v>
+        <f t="shared" ref="M5:M34" si="3">C5/L5</f>
+        <v>5.9859164951769408</v>
       </c>
       <c r="N5">
-        <v>0.155666</v>
+        <v>0.164075</v>
       </c>
       <c r="O5">
-        <v>0.113647</v>
+        <v>8.9487999999999998E-2</v>
       </c>
       <c r="P5">
-        <v>0.32985700000000001</v>
+        <v>0.32161899999999999</v>
       </c>
       <c r="Q5" s="11">
-        <f t="shared" ref="Q5:Q34" si="3">C5/P5</f>
-        <v>6.2736761687640401</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>6.5389482586538739</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>12000000</v>
       </c>
       <c r="B6">
-        <v>2.2632560000000002</v>
+        <v>2.2614899999999998</v>
       </c>
       <c r="C6" s="4">
-        <v>2.3373590000000002</v>
+        <v>2.3671989999999998</v>
       </c>
       <c r="D6">
         <v>0.28162700000000002</v>
@@ -2755,8 +2788,8 @@
         <v>0.36280200000000001</v>
       </c>
       <c r="F6" s="9">
-        <f t="shared" si="0"/>
-        <v>6.4425196112480085</v>
+        <f t="shared" si="1"/>
+        <v>6.5247683309353306</v>
       </c>
       <c r="G6">
         <v>0.157946</v>
@@ -2765,45 +2798,45 @@
         <v>0.23816200000000001</v>
       </c>
       <c r="I6" s="9">
-        <f t="shared" si="1"/>
-        <v>9.8141559106826453</v>
+        <f t="shared" si="2"/>
+        <v>9.9394487785624897</v>
       </c>
       <c r="J6">
-        <v>0.16986599999999999</v>
+        <v>0.19326599999999999</v>
       </c>
       <c r="K6">
-        <v>0.12692200000000001</v>
+        <v>9.5960000000000004E-2</v>
       </c>
       <c r="L6">
-        <v>0.37709300000000001</v>
+        <v>0.38957199999999997</v>
       </c>
       <c r="M6" s="9">
-        <f t="shared" si="2"/>
-        <v>6.1983622077312495</v>
+        <f t="shared" si="3"/>
+        <v>6.0764094955489618</v>
       </c>
       <c r="N6">
-        <v>0.188857</v>
+        <v>0.17265</v>
       </c>
       <c r="O6">
-        <v>0.113469</v>
+        <v>0.114621</v>
       </c>
       <c r="P6">
-        <v>0.37111300000000003</v>
+        <v>0.36581599999999997</v>
       </c>
       <c r="Q6" s="11">
-        <f t="shared" si="3"/>
-        <v>6.2982406975772882</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>6.4710100159643096</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>13000000</v>
       </c>
       <c r="B7">
-        <v>2.5330979999999998</v>
+        <v>2.531981</v>
       </c>
       <c r="C7" s="4">
-        <v>2.615335</v>
+        <v>2.6392120000000001</v>
       </c>
       <c r="D7">
         <v>0.344472</v>
@@ -2812,8 +2845,8 @@
         <v>0.42789899999999997</v>
       </c>
       <c r="F7" s="9">
-        <f t="shared" si="0"/>
-        <v>6.1120381211454111</v>
+        <f t="shared" si="1"/>
+        <v>6.1678386722100313</v>
       </c>
       <c r="G7">
         <v>0.17783599999999999</v>
@@ -2822,45 +2855,45 @@
         <v>0.26837800000000001</v>
       </c>
       <c r="I7" s="9">
-        <f t="shared" si="1"/>
-        <v>9.7449679183837716</v>
+        <f t="shared" si="2"/>
+        <v>9.833935717532734</v>
       </c>
       <c r="J7">
-        <v>0.18798300000000001</v>
+        <v>0.187859</v>
       </c>
       <c r="K7">
-        <v>0.13190499999999999</v>
+        <v>0.13759399999999999</v>
       </c>
       <c r="L7">
-        <v>0.40567199999999998</v>
+        <v>0.442241</v>
       </c>
       <c r="M7" s="9">
-        <f t="shared" si="2"/>
-        <v>6.446920171961585</v>
+        <f t="shared" si="3"/>
+        <v>5.967813929509024</v>
       </c>
       <c r="N7">
-        <v>0.18679899999999999</v>
+        <v>0.18529999999999999</v>
       </c>
       <c r="O7">
-        <v>0.13014899999999999</v>
+        <v>0.114091</v>
       </c>
       <c r="P7">
-        <v>0.39655899999999999</v>
+        <v>0.38733600000000001</v>
       </c>
       <c r="Q7" s="11">
-        <f t="shared" si="3"/>
-        <v>6.595071603468841</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>6.8137534337112999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>14000000</v>
       </c>
       <c r="B8">
-        <v>2.8135729999999999</v>
+        <v>2.8117640000000002</v>
       </c>
       <c r="C8" s="4">
-        <v>2.9030179999999999</v>
+        <v>2.9274079999999998</v>
       </c>
       <c r="D8">
         <v>0.35028900000000002</v>
@@ -2869,8 +2902,8 @@
         <v>0.43850699999999998</v>
       </c>
       <c r="F8" s="9">
-        <f t="shared" si="0"/>
-        <v>6.6202318321030225</v>
+        <f t="shared" si="1"/>
+        <v>6.6758523809198023</v>
       </c>
       <c r="G8">
         <v>0.193637</v>
@@ -2879,45 +2912,45 @@
         <v>0.29069600000000001</v>
       </c>
       <c r="I8" s="9">
-        <f t="shared" si="1"/>
-        <v>9.9864394418911839</v>
+        <f t="shared" si="2"/>
+        <v>10.070341525167184</v>
       </c>
       <c r="J8">
-        <v>0.21310999999999999</v>
+        <v>0.229714</v>
       </c>
       <c r="K8">
-        <v>0.12876899999999999</v>
+        <v>0.13857900000000001</v>
       </c>
       <c r="L8">
-        <v>0.43764399999999998</v>
+        <v>0.46689999999999998</v>
       </c>
       <c r="M8" s="9">
-        <f t="shared" si="2"/>
-        <v>6.6332864154426883</v>
+        <f t="shared" si="3"/>
+        <v>6.2698822017562641</v>
       </c>
       <c r="N8">
-        <v>0.206566</v>
+        <v>0.22131200000000001</v>
       </c>
       <c r="O8">
-        <v>0.134551</v>
+        <v>0.11294999999999999</v>
       </c>
       <c r="P8">
-        <v>0.42739199999999999</v>
+        <v>0.43114400000000003</v>
       </c>
       <c r="Q8" s="11">
-        <f t="shared" si="3"/>
-        <v>6.7924013551961666</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>6.7898613920175155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>15000000</v>
       </c>
       <c r="B9">
-        <v>3.1009039999999999</v>
+        <v>3.099081</v>
       </c>
       <c r="C9" s="4">
-        <v>3.1970649999999998</v>
+        <v>3.230092</v>
       </c>
       <c r="D9">
         <v>0.38580199999999998</v>
@@ -2926,8 +2959,8 @@
         <v>0.48250700000000002</v>
       </c>
       <c r="F9" s="9">
-        <f t="shared" si="0"/>
-        <v>6.6259453230730321</v>
+        <f t="shared" si="1"/>
+        <v>6.6943940709668457</v>
       </c>
       <c r="G9">
         <v>0.216415</v>
@@ -2936,45 +2969,45 @@
         <v>0.31031199999999998</v>
       </c>
       <c r="I9" s="9">
-        <f t="shared" si="1"/>
-        <v>10.302743690221455</v>
+        <f t="shared" si="2"/>
+        <v>10.409175281652015</v>
       </c>
       <c r="J9">
-        <v>0.22931599999999999</v>
+        <v>0.23347699999999999</v>
       </c>
       <c r="K9">
-        <v>0.13844600000000001</v>
+        <v>0.15329100000000001</v>
       </c>
       <c r="L9">
-        <v>0.46998600000000001</v>
+        <v>0.56874100000000005</v>
       </c>
       <c r="M9" s="9">
-        <f t="shared" si="2"/>
-        <v>6.8024685841705921</v>
+        <f t="shared" si="3"/>
+        <v>5.6793725087517863</v>
       </c>
       <c r="N9">
-        <v>0.23213200000000001</v>
+        <v>0.22994700000000001</v>
       </c>
       <c r="O9">
-        <v>0.147894</v>
+        <v>0.123031</v>
       </c>
       <c r="P9">
-        <v>0.46681299999999998</v>
+        <v>0.46369500000000002</v>
       </c>
       <c r="Q9" s="11">
-        <f t="shared" si="3"/>
-        <v>6.8487060129002408</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>6.9659841059317005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>16000000</v>
       </c>
       <c r="B10">
-        <v>3.3963649999999999</v>
+        <v>3.3963390000000002</v>
       </c>
       <c r="C10" s="4">
-        <v>3.4929329999999998</v>
+        <v>3.5315159999999999</v>
       </c>
       <c r="D10">
         <v>0.42282999999999998</v>
@@ -2983,8 +3016,8 @@
         <v>0.51977399999999996</v>
       </c>
       <c r="F10" s="9">
-        <f t="shared" si="0"/>
-        <v>6.7200995047847725</v>
+        <f t="shared" si="1"/>
+        <v>6.7943298433549968</v>
       </c>
       <c r="G10">
         <v>0.23191200000000001</v>
@@ -2993,45 +3026,45 @@
         <v>0.34072799999999998</v>
       </c>
       <c r="I10" s="9">
-        <f t="shared" si="1"/>
-        <v>10.251382334295979</v>
+        <f t="shared" si="2"/>
+        <v>10.364619285764599</v>
       </c>
       <c r="J10">
-        <v>0.25228099999999998</v>
+        <v>0.25047599999999998</v>
       </c>
       <c r="K10">
-        <v>0.219948</v>
+        <v>0.15142600000000001</v>
       </c>
       <c r="L10">
-        <v>0.60811199999999999</v>
+        <v>0.52703299999999997</v>
       </c>
       <c r="M10" s="9">
-        <f t="shared" si="2"/>
-        <v>5.7438975057226296</v>
+        <f t="shared" si="3"/>
+        <v>6.7007492889439559</v>
       </c>
       <c r="N10">
-        <v>0.26921899999999999</v>
+        <v>0.25673800000000002</v>
       </c>
       <c r="O10">
-        <v>0.18812999999999999</v>
+        <v>0.16491500000000001</v>
       </c>
       <c r="P10">
-        <v>0.53893599999999997</v>
+        <v>0.553338</v>
       </c>
       <c r="Q10" s="11">
-        <f t="shared" si="3"/>
-        <v>6.4811647394124723</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>6.3822040055083873</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>17000000</v>
       </c>
       <c r="B11">
-        <v>3.704088</v>
+        <v>3.7004570000000001</v>
       </c>
       <c r="C11" s="4">
-        <v>3.8080059999999998</v>
+        <v>3.8283680000000002</v>
       </c>
       <c r="D11">
         <v>0.46018900000000001</v>
@@ -3040,8 +3073,8 @@
         <v>0.56303700000000001</v>
       </c>
       <c r="F11" s="9">
-        <f t="shared" si="0"/>
-        <v>6.763331717098521</v>
+        <f t="shared" si="1"/>
+        <v>6.7994963030848776</v>
       </c>
       <c r="G11">
         <v>0.25092300000000001</v>
@@ -3050,45 +3083,45 @@
         <v>0.36224800000000001</v>
       </c>
       <c r="I11" s="9">
-        <f t="shared" si="1"/>
-        <v>10.512151895938693</v>
+        <f t="shared" si="2"/>
+        <v>10.568362006139441</v>
       </c>
       <c r="J11">
-        <v>0.27406900000000001</v>
+        <v>0.28723599999999999</v>
       </c>
       <c r="K11">
-        <v>0.160723</v>
+        <v>0.25220500000000001</v>
       </c>
       <c r="L11">
-        <v>0.56933199999999995</v>
+        <v>0.65071800000000002</v>
       </c>
       <c r="M11" s="9">
-        <f t="shared" si="2"/>
-        <v>6.688550792859</v>
+        <f t="shared" si="3"/>
+        <v>5.8832981414376118</v>
       </c>
       <c r="N11">
-        <v>0.287935</v>
+        <v>0.27944400000000003</v>
       </c>
       <c r="O11">
-        <v>0.15998200000000001</v>
+        <v>0.151396</v>
       </c>
       <c r="P11">
-        <v>0.55478499999999997</v>
+        <v>0.57420700000000002</v>
       </c>
       <c r="Q11" s="11">
-        <f t="shared" si="3"/>
-        <v>6.8639310723974152</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>6.6672262790248116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>18000000</v>
       </c>
       <c r="B12">
-        <v>4.0140180000000001</v>
+        <v>4.0108110000000003</v>
       </c>
       <c r="C12" s="4">
-        <v>4.1216989999999996</v>
+        <v>4.154458</v>
       </c>
       <c r="D12">
         <v>0.499305</v>
@@ -3097,8 +3130,8 @@
         <v>0.60928300000000002</v>
       </c>
       <c r="F12" s="9">
-        <f t="shared" si="0"/>
-        <v>6.7648350602265275</v>
+        <f t="shared" si="1"/>
+        <v>6.8186015365601857</v>
       </c>
       <c r="G12">
         <v>0.283526</v>
@@ -3107,45 +3140,45 @@
         <v>0.40043299999999998</v>
       </c>
       <c r="I12" s="9">
-        <f t="shared" si="1"/>
-        <v>10.293105213606271</v>
+        <f t="shared" si="2"/>
+        <v>10.374914155426751</v>
       </c>
       <c r="J12">
-        <v>0.30223</v>
+        <v>0.29866700000000002</v>
       </c>
       <c r="K12">
-        <v>0.17941799999999999</v>
+        <v>0.26340999999999998</v>
       </c>
       <c r="L12">
-        <v>0.62013499999999999</v>
+        <v>0.69674899999999995</v>
       </c>
       <c r="M12" s="9">
-        <f t="shared" si="2"/>
-        <v>6.6464544010578335</v>
+        <f t="shared" si="3"/>
+        <v>5.9626321673945712</v>
       </c>
       <c r="N12">
-        <v>0.324096</v>
+        <v>0.29756899999999997</v>
       </c>
       <c r="O12">
-        <v>0.172626</v>
+        <v>0.185693</v>
       </c>
       <c r="P12">
-        <v>0.59407900000000002</v>
+        <v>0.63354200000000005</v>
       </c>
       <c r="Q12" s="11">
-        <f t="shared" si="3"/>
-        <v>6.9379644794715842</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>6.5575099993370598</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>19000000</v>
       </c>
       <c r="B13">
-        <v>4.350587</v>
+        <v>4.3306940000000003</v>
       </c>
       <c r="C13" s="4">
-        <v>4.4633979999999998</v>
+        <v>4.4743740000000001</v>
       </c>
       <c r="D13">
         <v>0.53838399999999997</v>
@@ -3154,8 +3187,8 @@
         <v>0.65372799999999998</v>
       </c>
       <c r="F13" s="9">
-        <f t="shared" si="0"/>
-        <v>6.8276072005482398</v>
+        <f t="shared" si="1"/>
+        <v>6.8443970581036764</v>
       </c>
       <c r="G13">
         <v>0.29564000000000001</v>
@@ -3164,45 +3197,45 @@
         <v>0.41647200000000001</v>
       </c>
       <c r="I13" s="9">
-        <f t="shared" si="1"/>
-        <v>10.717162258207033</v>
+        <f t="shared" si="2"/>
+        <v>10.743516971128912</v>
       </c>
       <c r="J13">
-        <v>0.33587800000000001</v>
+        <v>0.33039000000000002</v>
       </c>
       <c r="K13">
-        <v>0.17507700000000001</v>
+        <v>0.16848299999999999</v>
       </c>
       <c r="L13">
-        <v>0.62832600000000005</v>
+        <v>0.626803</v>
       </c>
       <c r="M13" s="9">
-        <f t="shared" si="2"/>
-        <v>7.1036341007693453</v>
+        <f t="shared" si="3"/>
+        <v>7.1384055277335943</v>
       </c>
       <c r="N13">
-        <v>0.32130599999999998</v>
+        <v>0.32174999999999998</v>
       </c>
       <c r="O13">
-        <v>0.213007</v>
+        <v>0.168183</v>
       </c>
       <c r="P13">
-        <v>0.64873999999999998</v>
+        <v>0.62671500000000002</v>
       </c>
       <c r="Q13" s="11">
-        <f t="shared" si="3"/>
-        <v>6.8801029688318893</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>7.1394078648189367</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>20000000</v>
       </c>
       <c r="B14">
-        <v>4.6694050000000002</v>
+        <v>4.6921489999999997</v>
       </c>
       <c r="C14" s="4">
-        <v>4.7915530000000004</v>
+        <v>4.8425269999999996</v>
       </c>
       <c r="D14">
         <v>0.579681</v>
@@ -3211,8 +3244,8 @@
         <v>0.698766</v>
       </c>
       <c r="F14" s="9">
-        <f t="shared" si="0"/>
-        <v>6.8571639146724372</v>
+        <f t="shared" si="1"/>
+        <v>6.9301125126294059</v>
       </c>
       <c r="G14">
         <v>0.31309500000000001</v>
@@ -3221,45 +3254,45 @@
         <v>0.43568299999999999</v>
       </c>
       <c r="I14" s="9">
-        <f t="shared" si="1"/>
-        <v>10.997796563097483</v>
+        <f t="shared" si="2"/>
+        <v>11.11479447212767</v>
       </c>
       <c r="J14">
-        <v>0.368504</v>
+        <v>0.36140699999999998</v>
       </c>
       <c r="K14">
-        <v>0.164212</v>
+        <v>0.17725199999999999</v>
       </c>
       <c r="L14">
-        <v>0.66302700000000003</v>
+        <v>0.68197700000000006</v>
       </c>
       <c r="M14" s="9">
-        <f t="shared" si="2"/>
-        <v>7.2267841279465239</v>
+        <f t="shared" si="3"/>
+        <v>7.1007189392017604</v>
       </c>
       <c r="N14">
-        <v>0.347055</v>
+        <v>0.34512999999999999</v>
       </c>
       <c r="O14">
-        <v>0.185919</v>
+        <v>0.178616</v>
       </c>
       <c r="P14">
-        <v>0.660968</v>
+        <v>0.67111100000000001</v>
       </c>
       <c r="Q14" s="11">
-        <f t="shared" si="3"/>
-        <v>7.2492964863654521</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>7.2156871218025032</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>21000000</v>
       </c>
       <c r="B15">
-        <v>5.0074110000000003</v>
+        <v>4.991924</v>
       </c>
       <c r="C15" s="4">
-        <v>5.129543</v>
+        <v>5.1548030000000002</v>
       </c>
       <c r="D15">
         <v>0.64369600000000005</v>
@@ -3268,8 +3301,8 @@
         <v>0.76528300000000005</v>
       </c>
       <c r="F15" s="9">
-        <f t="shared" si="0"/>
-        <v>6.7028053674261674</v>
+        <f t="shared" si="1"/>
+        <v>6.7358127646896637</v>
       </c>
       <c r="G15">
         <v>0.331011</v>
@@ -3278,45 +3311,45 @@
         <v>0.46032200000000001</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" si="1"/>
-        <v>11.143380068734494</v>
+        <f t="shared" si="2"/>
+        <v>11.198254699970891</v>
       </c>
       <c r="J15">
-        <v>0.368591</v>
+        <v>0.37110599999999999</v>
       </c>
       <c r="K15">
-        <v>0.33624500000000002</v>
+        <v>0.18732299999999999</v>
       </c>
       <c r="L15">
-        <v>0.85542300000000004</v>
+        <v>0.72574499999999997</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" si="2"/>
-        <v>5.9964988081919701</v>
+        <f t="shared" si="3"/>
+        <v>7.1027743904539475</v>
       </c>
       <c r="N15">
-        <v>0.37243799999999999</v>
+        <v>0.37145600000000001</v>
       </c>
       <c r="O15">
-        <v>0.23216500000000001</v>
+        <v>0.40421000000000001</v>
       </c>
       <c r="P15">
-        <v>0.73946699999999999</v>
+        <v>0.92356700000000003</v>
       </c>
       <c r="Q15" s="11">
-        <f t="shared" si="3"/>
-        <v>6.9368112437742324</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>5.5814066548501629</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>22000000</v>
       </c>
       <c r="B16">
-        <v>5.3761010000000002</v>
+        <v>5.3300989999999997</v>
       </c>
       <c r="C16" s="4">
-        <v>5.5324220000000004</v>
+        <v>5.5227000000000004</v>
       </c>
       <c r="D16">
         <v>0.67809900000000001</v>
@@ -3325,8 +3358,8 @@
         <v>0.80962599999999996</v>
       </c>
       <c r="F16" s="9">
-        <f t="shared" si="0"/>
-        <v>6.8333057485802096</v>
+        <f t="shared" si="1"/>
+        <v>6.8212977350035704</v>
       </c>
       <c r="G16">
         <v>0.35961100000000001</v>
@@ -3335,34 +3368,34 @@
         <v>0.49295099999999997</v>
       </c>
       <c r="I16" s="9">
-        <f t="shared" si="1"/>
-        <v>11.223066795685577</v>
+        <f t="shared" si="2"/>
+        <v>11.203344754346782</v>
       </c>
       <c r="J16">
-        <v>0.39257500000000001</v>
+        <v>0.39402999999999999</v>
       </c>
       <c r="K16">
-        <v>0.19891800000000001</v>
+        <v>0.22459499999999999</v>
       </c>
       <c r="L16">
-        <v>0.75799300000000003</v>
+        <v>0.79874000000000001</v>
       </c>
       <c r="M16" s="9">
-        <f t="shared" si="2"/>
-        <v>7.2987771654883362</v>
+        <f t="shared" si="3"/>
+        <v>6.9142649673235352</v>
       </c>
       <c r="N16">
-        <v>0.39258399999999999</v>
+        <v>0.39453300000000002</v>
       </c>
       <c r="O16">
-        <v>0.188501</v>
+        <v>0.193055</v>
       </c>
       <c r="P16">
-        <v>0.71789000000000003</v>
+        <v>0.74716899999999997</v>
       </c>
       <c r="Q16" s="11">
-        <f t="shared" si="3"/>
-        <v>7.7065037819164495</v>
+        <f t="shared" si="0"/>
+        <v>7.3915004503666513</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
@@ -3370,10 +3403,10 @@
         <v>23000000</v>
       </c>
       <c r="B17">
-        <v>5.6839029999999999</v>
+        <v>5.6791049999999998</v>
       </c>
       <c r="C17" s="4">
-        <v>5.8111759999999997</v>
+        <v>5.8535399999999997</v>
       </c>
       <c r="D17">
         <v>0.724553</v>
@@ -3382,8 +3415,8 @@
         <v>0.85989400000000005</v>
       </c>
       <c r="F17" s="9">
-        <f t="shared" si="0"/>
-        <v>6.7580143599094766</v>
+        <f t="shared" si="1"/>
+        <v>6.8072808974129364</v>
       </c>
       <c r="G17">
         <v>0.382579</v>
@@ -3392,34 +3425,34 @@
         <v>0.52661000000000002</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" si="1"/>
-        <v>11.035065798218795</v>
+        <f t="shared" si="2"/>
+        <v>11.115512428552439</v>
       </c>
       <c r="J17">
-        <v>0.41992099999999999</v>
+        <v>0.44333099999999998</v>
       </c>
       <c r="K17">
-        <v>0.202066</v>
+        <v>0.180732</v>
       </c>
       <c r="L17">
-        <v>0.79306299999999996</v>
+        <v>0.79464500000000005</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="2"/>
-        <v>7.3275086594633718</v>
+        <f t="shared" si="3"/>
+        <v>7.3662327202713156</v>
       </c>
       <c r="N17">
-        <v>0.41874600000000001</v>
+        <v>0.43036099999999999</v>
       </c>
       <c r="O17">
-        <v>0.55584299999999998</v>
+        <v>0.23480100000000001</v>
       </c>
       <c r="P17">
-        <v>1.1124590000000001</v>
+        <v>0.81858600000000004</v>
       </c>
       <c r="Q17" s="11">
-        <f t="shared" si="3"/>
-        <v>5.2237215034441711</v>
+        <f t="shared" si="0"/>
+        <v>7.15079417434454</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
@@ -3427,10 +3460,10 @@
         <v>24000000</v>
       </c>
       <c r="B18">
-        <v>6.0344829999999998</v>
+        <v>6.0303909999999998</v>
       </c>
       <c r="C18" s="4">
-        <v>6.1727420000000004</v>
+        <v>6.2170909999999999</v>
       </c>
       <c r="D18">
         <v>0.75098500000000001</v>
@@ -3439,8 +3472,8 @@
         <v>0.89380300000000001</v>
       </c>
       <c r="F18" s="9">
-        <f t="shared" si="0"/>
-        <v>6.9061549357073098</v>
+        <f t="shared" si="1"/>
+        <v>6.9557732520477105</v>
       </c>
       <c r="G18">
         <v>0.40873399999999999</v>
@@ -3449,34 +3482,34 @@
         <v>0.55763099999999999</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="1"/>
-        <v>11.069581856101975</v>
+        <f t="shared" si="2"/>
+        <v>11.149112943864312</v>
       </c>
       <c r="J18">
-        <v>0.44379099999999999</v>
+        <v>0.47020600000000001</v>
       </c>
       <c r="K18">
-        <v>0.21997700000000001</v>
+        <v>0.21249599999999999</v>
       </c>
       <c r="L18">
-        <v>0.83222399999999996</v>
+        <v>0.86087199999999997</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="2"/>
-        <v>7.417164128888377</v>
+        <f t="shared" si="3"/>
+        <v>7.2218529583956732</v>
       </c>
       <c r="N18">
-        <v>0.44661200000000001</v>
+        <v>0.45207199999999997</v>
       </c>
       <c r="O18">
-        <v>0.20712</v>
+        <v>0.19564100000000001</v>
       </c>
       <c r="P18">
-        <v>0.800902</v>
+        <v>0.81842599999999999</v>
       </c>
       <c r="Q18" s="11">
-        <f t="shared" si="3"/>
-        <v>7.7072375896177068</v>
+        <f t="shared" si="0"/>
+        <v>7.5963996744971443</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
@@ -3484,10 +3517,10 @@
         <v>25000000</v>
       </c>
       <c r="B19">
-        <v>6.4007149999999999</v>
+        <v>6.3905620000000001</v>
       </c>
       <c r="C19" s="4">
-        <v>6.5400400000000003</v>
+        <v>6.5945340000000003</v>
       </c>
       <c r="D19">
         <v>0.79549800000000004</v>
@@ -3496,8 +3529,8 @@
         <v>0.93919399999999997</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="0"/>
-        <v>6.9634601583911317</v>
+        <f t="shared" si="1"/>
+        <v>7.0214822496736566</v>
       </c>
       <c r="G19">
         <v>0.427782</v>
@@ -3506,34 +3539,34 @@
         <v>0.58167100000000005</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="1"/>
-        <v>11.243538013756917</v>
+        <f t="shared" si="2"/>
+        <v>11.337223275700525</v>
       </c>
       <c r="J19">
-        <v>0.48261799999999999</v>
+        <v>0.48530000000000001</v>
       </c>
       <c r="K19">
-        <v>0.22817299999999999</v>
+        <v>0.202236</v>
       </c>
       <c r="L19">
-        <v>0.88471299999999997</v>
+        <v>0.895146</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="2"/>
-        <v>7.3922729743996083</v>
+        <f t="shared" si="3"/>
+        <v>7.3669926470095382</v>
       </c>
       <c r="N19">
-        <v>0.474331</v>
+        <v>0.478468</v>
       </c>
       <c r="O19">
-        <v>0.221802</v>
+        <v>0.19278699999999999</v>
       </c>
       <c r="P19">
-        <v>0.84991899999999998</v>
+        <v>0.85243400000000003</v>
       </c>
       <c r="Q19" s="11">
-        <f t="shared" si="3"/>
-        <v>7.6948979843961602</v>
+        <f t="shared" si="0"/>
+        <v>7.7361226792924729</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
@@ -3541,10 +3574,10 @@
         <v>26000000</v>
       </c>
       <c r="B20">
-        <v>6.7587020000000004</v>
+        <v>6.7549650000000003</v>
       </c>
       <c r="C20" s="4">
-        <v>6.9036559999999998</v>
+        <v>6.9617089999999999</v>
       </c>
       <c r="D20">
         <v>0.84600600000000004</v>
@@ -3553,8 +3586,8 @@
         <v>0.99577599999999999</v>
       </c>
       <c r="F20" s="9">
-        <f t="shared" si="0"/>
-        <v>6.932940741692911</v>
+        <f t="shared" si="1"/>
+        <v>6.9912399977504984</v>
       </c>
       <c r="G20">
         <v>0.45273600000000003</v>
@@ -3563,34 +3596,34 @@
         <v>0.61212200000000005</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="1"/>
-        <v>11.278235384449504</v>
+        <f t="shared" si="2"/>
+        <v>11.373074321785525</v>
       </c>
       <c r="J20">
-        <v>0.55763099999999999</v>
+        <v>0.50156599999999996</v>
       </c>
       <c r="K20">
-        <v>0.25181399999999998</v>
+        <v>0.236147</v>
       </c>
       <c r="L20">
-        <v>0.91830299999999998</v>
+        <v>0.93239899999999998</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="2"/>
-        <v>7.5178410611747974</v>
+        <f t="shared" si="3"/>
+        <v>7.4664483767142604</v>
       </c>
       <c r="N20">
-        <v>0.49525200000000003</v>
+        <v>0.512262</v>
       </c>
       <c r="O20">
-        <v>0.23372899999999999</v>
+        <v>0.24243600000000001</v>
       </c>
       <c r="P20">
-        <v>0.88633399999999996</v>
+        <v>0.92390399999999995</v>
       </c>
       <c r="Q20" s="11">
-        <f t="shared" si="3"/>
-        <v>7.7890005347871121</v>
+        <f t="shared" si="0"/>
+        <v>7.5350999670961487</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
@@ -3598,10 +3631,10 @@
         <v>27000000</v>
       </c>
       <c r="B21">
-        <v>7.1340120000000002</v>
+        <v>7.1282779999999999</v>
       </c>
       <c r="C21" s="4">
-        <v>7.2841440000000004</v>
+        <v>7.322921</v>
       </c>
       <c r="D21">
         <v>0.91964100000000004</v>
@@ -3610,8 +3643,8 @@
         <v>1.0891120000000001</v>
       </c>
       <c r="F21" s="9">
-        <f t="shared" si="0"/>
-        <v>6.6881496117938282</v>
+        <f t="shared" si="1"/>
+        <v>6.7237538471709053</v>
       </c>
       <c r="G21">
         <v>0.47664200000000001</v>
@@ -3620,34 +3653,34 @@
         <v>0.63880199999999998</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="1"/>
-        <v>11.402819653038032</v>
+        <f t="shared" si="2"/>
+        <v>11.463522343386527</v>
       </c>
       <c r="J21">
-        <v>0.529972</v>
+        <v>0.53628699999999996</v>
       </c>
       <c r="K21">
-        <v>0.23668700000000001</v>
+        <v>0.217556</v>
       </c>
       <c r="L21">
-        <v>0.92722800000000005</v>
+        <v>0.920678</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="2"/>
-        <v>7.8558283399552211</v>
+        <f t="shared" si="3"/>
+        <v>7.953835108474407</v>
       </c>
       <c r="N21">
-        <v>0.52453499999999997</v>
+        <v>0.52862699999999996</v>
       </c>
       <c r="O21">
-        <v>0.26279400000000003</v>
+        <v>0.20550399999999999</v>
       </c>
       <c r="P21">
-        <v>0.95094800000000002</v>
+        <v>0.92293899999999995</v>
       </c>
       <c r="Q21" s="11">
-        <f t="shared" si="3"/>
-        <v>7.6598762498054578</v>
+        <f t="shared" si="0"/>
+        <v>7.9343499407869862</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
@@ -3655,10 +3688,10 @@
         <v>28000000</v>
       </c>
       <c r="B22">
-        <v>7.5322800000000001</v>
+        <v>7.5052719999999997</v>
       </c>
       <c r="C22" s="4">
-        <v>7.6895899999999999</v>
+        <v>7.7059360000000003</v>
       </c>
       <c r="D22">
         <v>0.94684999999999997</v>
@@ -3667,8 +3700,8 @@
         <v>1.1164970000000001</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="0"/>
-        <v>6.88724645028155</v>
+        <f t="shared" si="1"/>
+        <v>6.9018868837085989</v>
       </c>
       <c r="G22">
         <v>0.50634800000000002</v>
@@ -3677,34 +3710,34 @@
         <v>0.67689500000000002</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="1"/>
-        <v>11.360092776575392</v>
+        <f t="shared" si="2"/>
+        <v>11.38424127818938</v>
       </c>
       <c r="J22">
-        <v>0.554091</v>
+        <v>0.56313800000000003</v>
       </c>
       <c r="K22">
-        <v>0.27377099999999999</v>
+        <v>0.21976499999999999</v>
       </c>
       <c r="L22">
-        <v>1.0077050000000001</v>
+        <v>0.96872599999999998</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="2"/>
-        <v>7.6307947266313052</v>
+        <f t="shared" si="3"/>
+        <v>7.9547116522112553</v>
       </c>
       <c r="N22">
-        <v>0.55939399999999995</v>
+        <v>0.56069800000000003</v>
       </c>
       <c r="O22">
-        <v>0.25787599999999999</v>
+        <v>0.25718099999999999</v>
       </c>
       <c r="P22">
-        <v>1.0019979999999999</v>
+        <v>0.98792500000000005</v>
       </c>
       <c r="Q22" s="11">
-        <f t="shared" si="3"/>
-        <v>7.6742568348439821</v>
+        <f t="shared" si="0"/>
+        <v>7.8001224789331172</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
@@ -3712,10 +3745,10 @@
         <v>29000000</v>
       </c>
       <c r="B23">
-        <v>7.8925739999999998</v>
+        <v>7.8874610000000001</v>
       </c>
       <c r="C23" s="4">
-        <v>8.0493690000000004</v>
+        <v>8.0842749999999999</v>
       </c>
       <c r="D23">
         <v>0.99387499999999995</v>
@@ -3724,8 +3757,8 @@
         <v>1.166188</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="0"/>
-        <v>6.9022910542725535</v>
+        <f t="shared" si="1"/>
+        <v>6.9322227633966396</v>
       </c>
       <c r="G23">
         <v>0.52846199999999999</v>
@@ -3734,34 +3767,34 @@
         <v>0.70352300000000001</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="1"/>
-        <v>11.44151506063057</v>
+        <f t="shared" si="2"/>
+        <v>11.491131064656024</v>
       </c>
       <c r="J23">
-        <v>0.58896499999999996</v>
+        <v>0.58981799999999995</v>
       </c>
       <c r="K23">
-        <v>0.24702099999999999</v>
+        <v>0.25647399999999998</v>
       </c>
       <c r="L23">
-        <v>1.0035540000000001</v>
+        <v>1.0602940000000001</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="2"/>
-        <v>8.020862853418949</v>
+        <f t="shared" si="3"/>
+        <v>7.6245597919067727</v>
       </c>
       <c r="N23">
-        <v>0.58512699999999995</v>
+        <v>0.580515</v>
       </c>
       <c r="O23">
-        <v>0.27720699999999998</v>
+        <v>0.25049399999999999</v>
       </c>
       <c r="P23">
-        <v>1.0420670000000001</v>
+        <v>1.045582</v>
       </c>
       <c r="Q23" s="11">
-        <f t="shared" si="3"/>
-        <v>7.7244255887577289</v>
+        <f t="shared" si="0"/>
+        <v>7.7318421701980329</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
@@ -3769,10 +3802,10 @@
         <v>30000000</v>
       </c>
       <c r="B24">
-        <v>8.2831829999999993</v>
+        <v>8.2786139999999993</v>
       </c>
       <c r="C24" s="4">
-        <v>8.4482809999999997</v>
+        <v>8.4775270000000003</v>
       </c>
       <c r="D24">
         <v>1.0478019999999999</v>
@@ -3781,8 +3814,8 @@
         <v>1.227876</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="0"/>
-        <v>6.8804024184852546</v>
+        <f t="shared" si="1"/>
+        <v>6.9042207845091852</v>
       </c>
       <c r="G24">
         <v>0.55159000000000002</v>
@@ -3791,34 +3824,34 @@
         <v>0.72828099999999996</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="1"/>
-        <v>11.600304003537097</v>
+        <f t="shared" si="2"/>
+        <v>11.640461580076922</v>
       </c>
       <c r="J24">
-        <v>0.61443099999999995</v>
+        <v>0.627085</v>
       </c>
       <c r="K24">
-        <v>0.25764300000000001</v>
+        <v>0.22342300000000001</v>
       </c>
       <c r="L24">
-        <v>1.04569</v>
+        <v>1.115772</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="2"/>
-        <v>8.0791448708508256</v>
+        <f t="shared" si="3"/>
+        <v>7.5979026180976046</v>
       </c>
       <c r="N24">
-        <v>0.614811</v>
+        <v>0.62524800000000003</v>
       </c>
       <c r="O24">
-        <v>0.23727699999999999</v>
+        <v>0.29843799999999998</v>
       </c>
       <c r="P24">
-        <v>1.0274939999999999</v>
+        <v>1.152817</v>
       </c>
       <c r="Q24" s="11">
-        <f t="shared" si="3"/>
-        <v>8.2222193024971446</v>
+        <f t="shared" si="0"/>
+        <v>7.3537491206323296</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
@@ -3826,10 +3859,10 @@
         <v>31000000</v>
       </c>
       <c r="B25">
-        <v>8.6693409999999993</v>
+        <v>8.7138349999999996</v>
       </c>
       <c r="C25" s="4">
-        <v>9.0488359999999997</v>
+        <v>8.9261719999999993</v>
       </c>
       <c r="D25">
         <v>1.091896</v>
@@ -3838,8 +3871,8 @@
         <v>1.2760750000000001</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="0"/>
-        <v>7.091147463902983</v>
+        <f t="shared" si="1"/>
+        <v>6.9950214525008318</v>
       </c>
       <c r="G25">
         <v>0.57734600000000003</v>
@@ -3848,34 +3881,34 @@
         <v>0.761297</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="1"/>
-        <v>11.886078626344252</v>
+        <f t="shared" si="2"/>
+        <v>11.724953598923941</v>
       </c>
       <c r="J25">
-        <v>0.64282399999999995</v>
+        <v>0.66337100000000004</v>
       </c>
       <c r="K25">
-        <v>0.27227000000000001</v>
+        <v>0.271125</v>
       </c>
       <c r="L25">
-        <v>1.093251</v>
+        <v>1.1492789999999999</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="2"/>
-        <v>8.2769976885454479</v>
+        <f t="shared" si="3"/>
+        <v>7.7667581153053344</v>
       </c>
       <c r="N25">
-        <v>0.63736899999999996</v>
+        <v>0.644459</v>
       </c>
       <c r="O25">
-        <v>0.59015899999999999</v>
+        <v>0.233075</v>
       </c>
       <c r="P25">
-        <v>1.418671</v>
+        <v>1.112115</v>
       </c>
       <c r="Q25" s="11">
-        <f t="shared" si="3"/>
-        <v>6.3783893517242545</v>
+        <f t="shared" si="0"/>
+        <v>8.0263030352076896</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
@@ -3883,10 +3916,10 @@
         <v>32000000</v>
       </c>
       <c r="B26">
-        <v>9.0744710000000008</v>
+        <v>9.0826989999999999</v>
       </c>
       <c r="C26" s="4">
-        <v>9.2498570000000004</v>
+        <v>9.2956199999999995</v>
       </c>
       <c r="D26">
         <v>1.1460250000000001</v>
@@ -3895,8 +3928,8 @@
         <v>1.3348279999999999</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="0"/>
-        <v>6.9296246407776891</v>
+        <f t="shared" si="1"/>
+        <v>6.9639084586178894</v>
       </c>
       <c r="G26">
         <v>0.61293299999999995</v>
@@ -3905,34 +3938,34 @@
         <v>0.80493999999999999</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="1"/>
-        <v>11.491362089099809</v>
+        <f t="shared" si="2"/>
+        <v>11.548214773771958</v>
       </c>
       <c r="J26">
-        <v>0.67550500000000002</v>
+        <v>0.672543</v>
       </c>
       <c r="K26">
-        <v>0.26855899999999999</v>
+        <v>0.26406600000000002</v>
       </c>
       <c r="L26">
-        <v>1.138903</v>
+        <v>1.202148</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="2"/>
-        <v>8.1217250283825759</v>
+        <f t="shared" si="3"/>
+        <v>7.7325088092314749</v>
       </c>
       <c r="N26">
-        <v>0.66696299999999997</v>
+        <v>0.67047699999999999</v>
       </c>
       <c r="O26">
-        <v>0.254554</v>
+        <v>0.258687</v>
       </c>
       <c r="P26">
-        <v>1.1193360000000001</v>
+        <v>1.1586460000000001</v>
       </c>
       <c r="Q26" s="11">
-        <f t="shared" si="3"/>
-        <v>8.263700086479842</v>
+        <f t="shared" si="0"/>
+        <v>8.0228300965091996</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
@@ -3940,10 +3973,10 @@
         <v>33000000</v>
       </c>
       <c r="B27">
-        <v>9.4827980000000007</v>
+        <v>9.5072290000000006</v>
       </c>
       <c r="C27" s="4">
-        <v>9.6635200000000001</v>
+        <v>9.7146369999999997</v>
       </c>
       <c r="D27">
         <v>1.26888</v>
@@ -3952,8 +3985,8 @@
         <v>1.4667490000000001</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" si="0"/>
-        <v>6.5883937878941792</v>
+        <f t="shared" si="1"/>
+        <v>6.6232443315113896</v>
       </c>
       <c r="G27">
         <v>0.63168899999999994</v>
@@ -3962,34 +3995,34 @@
         <v>0.82907299999999995</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="1"/>
-        <v>11.655813179297843</v>
+        <f t="shared" si="2"/>
+        <v>11.717468787428851</v>
       </c>
       <c r="J27">
-        <v>0.70679999999999998</v>
+        <v>0.72667400000000004</v>
       </c>
       <c r="K27">
-        <v>0.25460100000000002</v>
+        <v>0.296962</v>
       </c>
       <c r="L27">
-        <v>1.174553</v>
+        <v>1.2120230000000001</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="2"/>
-        <v>8.227402254304403</v>
+        <f t="shared" si="3"/>
+        <v>8.0152249586022695</v>
       </c>
       <c r="N27">
-        <v>0.69404299999999997</v>
+        <v>0.71296899999999996</v>
       </c>
       <c r="O27">
-        <v>0.28634900000000002</v>
+        <v>0.28098499999999998</v>
       </c>
       <c r="P27">
-        <v>1.176353</v>
+        <v>1.2481009999999999</v>
       </c>
       <c r="Q27" s="11">
-        <f t="shared" si="3"/>
-        <v>8.2148130705664038</v>
+        <f t="shared" si="0"/>
+        <v>7.7835343453774977</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
@@ -3997,10 +4030,10 @@
         <v>34000000</v>
       </c>
       <c r="B28">
-        <v>9.8909179999999992</v>
+        <v>9.888261</v>
       </c>
       <c r="C28" s="4">
-        <v>10.071818</v>
+        <v>10.095466</v>
       </c>
       <c r="D28">
         <v>1.2431160000000001</v>
@@ -4009,8 +4042,8 @@
         <v>1.442761</v>
       </c>
       <c r="F28" s="9">
-        <f t="shared" si="0"/>
-        <v>6.9809330859373109</v>
+        <f t="shared" si="1"/>
+        <v>6.9973238810863343</v>
       </c>
       <c r="G28">
         <v>0.66261300000000001</v>
@@ -4019,34 +4052,34 @@
         <v>0.87080400000000002</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="1"/>
-        <v>11.566113614544721</v>
+        <f t="shared" si="2"/>
+        <v>11.59327012737654</v>
       </c>
       <c r="J28">
-        <v>0.74298399999999998</v>
+        <v>0.74124800000000002</v>
       </c>
       <c r="K28">
-        <v>0.25919999999999999</v>
+        <v>0.30798300000000001</v>
       </c>
       <c r="L28">
-        <v>1.1881390000000001</v>
+        <v>1.343232</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="2"/>
-        <v>8.4769694454941718</v>
+        <f t="shared" si="3"/>
+        <v>7.5158021845816663</v>
       </c>
       <c r="N28">
-        <v>0.72564600000000001</v>
+        <v>0.75077300000000002</v>
       </c>
       <c r="O28">
-        <v>0.28007399999999999</v>
+        <v>0.26050499999999999</v>
       </c>
       <c r="P28">
-        <v>1.201994</v>
+        <v>1.2219789999999999</v>
       </c>
       <c r="Q28" s="11">
-        <f t="shared" si="3"/>
-        <v>8.3792581327361031</v>
+        <f t="shared" si="0"/>
+        <v>8.2615707798579194</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
@@ -4054,10 +4087,10 @@
         <v>35000000</v>
       </c>
       <c r="B29">
-        <v>10.305394</v>
+        <v>10.361186999999999</v>
       </c>
       <c r="C29" s="4">
-        <v>10.490605</v>
+        <v>10.571692000000001</v>
       </c>
       <c r="D29">
         <v>1.2956270000000001</v>
@@ -4066,8 +4099,8 @@
         <v>1.4959789999999999</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="0"/>
-        <v>7.012534935316606</v>
+        <f t="shared" si="1"/>
+        <v>7.0667382362987725</v>
       </c>
       <c r="G29">
         <v>0.68512399999999996</v>
@@ -4076,34 +4109,34 @@
         <v>0.89688699999999999</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="1"/>
-        <v>11.696685312642508</v>
+        <f t="shared" si="2"/>
+        <v>11.787094695318363</v>
       </c>
       <c r="J29">
-        <v>0.75991200000000003</v>
+        <v>0.759544</v>
       </c>
       <c r="K29">
-        <v>0.274258</v>
+        <v>0.26486599999999999</v>
       </c>
       <c r="L29">
-        <v>1.2491639999999999</v>
+        <v>1.2783770000000001</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="2"/>
-        <v>8.3981006497145305</v>
+        <f t="shared" si="3"/>
+        <v>8.2696199947276892</v>
       </c>
       <c r="N29">
-        <v>0.75389499999999998</v>
+        <v>0.76310999999999996</v>
       </c>
       <c r="O29">
-        <v>0.34645799999999999</v>
+        <v>0.29046699999999998</v>
       </c>
       <c r="P29">
-        <v>1.3217049999999999</v>
+        <v>1.2952410000000001</v>
       </c>
       <c r="Q29" s="11">
-        <f t="shared" si="3"/>
-        <v>7.9371758448367835</v>
+        <f t="shared" si="0"/>
+        <v>8.1619497838626174</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
@@ -4111,10 +4144,10 @@
         <v>36000000</v>
       </c>
       <c r="B30">
-        <v>10.728438000000001</v>
+        <v>10.91563</v>
       </c>
       <c r="C30" s="4">
-        <v>10.924785</v>
+        <v>11.142515</v>
       </c>
       <c r="D30">
         <v>1.345156</v>
@@ -4123,8 +4156,8 @@
         <v>1.554657</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="0"/>
-        <v>7.0271352459095482</v>
+        <f t="shared" si="1"/>
+        <v>7.167185430612669</v>
       </c>
       <c r="G30">
         <v>0.720723</v>
@@ -4133,34 +4166,34 @@
         <v>0.93816900000000003</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" si="1"/>
-        <v>11.644794274805498</v>
+        <f t="shared" si="2"/>
+        <v>11.876873996049751</v>
       </c>
       <c r="J30">
-        <v>0.82814200000000004</v>
+        <v>0.79788199999999998</v>
       </c>
       <c r="K30">
-        <v>0.30310799999999999</v>
+        <v>0.29107899999999998</v>
       </c>
       <c r="L30">
-        <v>1.340222</v>
+        <v>1.3376049999999999</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="2"/>
-        <v>8.1514741587587718</v>
+        <f t="shared" si="3"/>
+        <v>8.3301983769498467</v>
       </c>
       <c r="N30">
-        <v>0.78988100000000006</v>
+        <v>0.80297399999999997</v>
       </c>
       <c r="O30">
-        <v>0.27956500000000001</v>
+        <v>0.29154999999999998</v>
       </c>
       <c r="P30">
-        <v>1.2844789999999999</v>
+        <v>1.32508</v>
       </c>
       <c r="Q30" s="11">
-        <f t="shared" si="3"/>
-        <v>8.5052266327437049</v>
+        <f t="shared" si="0"/>
+        <v>8.408937573580463</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
@@ -4168,10 +4201,10 @@
         <v>37000000</v>
       </c>
       <c r="B31">
-        <v>11.154876</v>
+        <v>11.149357</v>
       </c>
       <c r="C31" s="4">
-        <v>11.349926999999999</v>
+        <v>11.384838999999999</v>
       </c>
       <c r="D31">
         <v>1.4055679999999999</v>
@@ -4180,8 +4213,8 @@
         <v>1.6190869999999999</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="0"/>
-        <v>7.0100785195607154</v>
+        <f t="shared" si="1"/>
+        <v>7.0316412891957008</v>
       </c>
       <c r="G31">
         <v>0.76413900000000001</v>
@@ -4190,34 +4223,34 @@
         <v>0.98982899999999996</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="1"/>
-        <v>11.466553313754194</v>
+        <f t="shared" si="2"/>
+        <v>11.501824052437341</v>
       </c>
       <c r="J31">
-        <v>0.83148699999999998</v>
+        <v>0.82260699999999998</v>
       </c>
       <c r="K31">
-        <v>0.28910599999999997</v>
+        <v>0.31930199999999997</v>
       </c>
       <c r="L31">
-        <v>1.334036</v>
+        <v>1.3924650000000001</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="2"/>
-        <v>8.5079615542609037</v>
+        <f t="shared" si="3"/>
+        <v>8.1760324316948711</v>
       </c>
       <c r="N31">
-        <v>0.81633100000000003</v>
+        <v>0.82231699999999996</v>
       </c>
       <c r="O31">
-        <v>0.28081099999999998</v>
+        <v>0.32889400000000002</v>
       </c>
       <c r="P31">
-        <v>1.3131120000000001</v>
+        <v>1.4191320000000001</v>
       </c>
       <c r="Q31" s="11">
-        <f t="shared" si="3"/>
-        <v>8.6435330725787285</v>
+        <f t="shared" si="0"/>
+        <v>8.0223960843670632</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
@@ -4225,10 +4258,10 @@
         <v>38000000</v>
       </c>
       <c r="B32">
-        <v>11.583615</v>
+        <v>11.578430000000001</v>
       </c>
       <c r="C32" s="4">
-        <v>11.785626000000001</v>
+        <v>11.813434000000001</v>
       </c>
       <c r="D32">
         <v>1.456799</v>
@@ -4237,8 +4270,8 @@
         <v>1.678501</v>
       </c>
       <c r="F32" s="9">
-        <f t="shared" si="0"/>
-        <v>7.0215186049933846</v>
+        <f t="shared" si="1"/>
+        <v>7.0380857681943594</v>
       </c>
       <c r="G32">
         <v>0.773424</v>
@@ -4247,45 +4280,45 @@
         <v>1.0039940000000001</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="1"/>
-        <v>11.73874146658247</v>
+        <f t="shared" si="2"/>
+        <v>11.766438843260019</v>
       </c>
       <c r="J32">
-        <v>0.84926500000000005</v>
+        <v>0.85871200000000003</v>
       </c>
       <c r="K32">
-        <v>0.30568200000000001</v>
+        <v>0.37237700000000001</v>
       </c>
       <c r="L32">
-        <v>1.39333</v>
+        <v>1.488686</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="2"/>
-        <v>8.4586034894820337</v>
+        <f t="shared" si="3"/>
+        <v>7.9354773269850067</v>
       </c>
       <c r="N32">
-        <v>0.85241500000000003</v>
+        <v>0.853016</v>
       </c>
       <c r="O32">
-        <v>0.731603</v>
+        <v>0.361595</v>
       </c>
       <c r="P32">
-        <v>1.810543</v>
+        <v>1.48349</v>
       </c>
       <c r="Q32" s="11">
-        <f t="shared" si="3"/>
-        <v>6.5094427472863119</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>7.963271744332622</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>39000000</v>
       </c>
       <c r="B33">
-        <v>12.019949</v>
+        <v>12.013828</v>
       </c>
       <c r="C33" s="4">
-        <v>12.22382</v>
+        <v>12.281571</v>
       </c>
       <c r="D33">
         <v>1.5234430000000001</v>
@@ -4294,8 +4327,8 @@
         <v>1.749349</v>
       </c>
       <c r="F33" s="9">
-        <f t="shared" si="0"/>
-        <v>6.987639401857491</v>
+        <f t="shared" si="1"/>
+        <v>7.0206522540670839</v>
       </c>
       <c r="G33">
         <v>0.80978899999999998</v>
@@ -4304,45 +4337,45 @@
         <v>1.0395719999999999</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="1"/>
-        <v>11.75851215692612</v>
+        <f t="shared" si="2"/>
+        <v>11.814064826678672</v>
       </c>
       <c r="J33">
-        <v>0.89504600000000001</v>
+        <v>0.96537600000000001</v>
       </c>
       <c r="K33">
-        <v>0.32373200000000002</v>
+        <v>0.29770099999999999</v>
       </c>
       <c r="L33">
-        <v>1.46035</v>
+        <v>1.5088649999999999</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="2"/>
-        <v>8.3704728318553769</v>
+        <f t="shared" si="3"/>
+        <v>8.1396089113340171</v>
       </c>
       <c r="N33">
-        <v>0.87834400000000001</v>
+        <v>0.92100199999999999</v>
       </c>
       <c r="O33">
-        <v>0.31311299999999997</v>
+        <v>0.27014500000000002</v>
       </c>
       <c r="P33">
-        <v>1.422147</v>
+        <v>1.585299</v>
       </c>
       <c r="Q33" s="11">
-        <f t="shared" si="3"/>
-        <v>8.5953280497726325</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>7.7471637842451164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>40000000</v>
       </c>
       <c r="B34">
-        <v>12.463679000000001</v>
+        <v>12.462076</v>
       </c>
       <c r="C34" s="4">
-        <v>12.674329999999999</v>
+        <v>12.756418</v>
       </c>
       <c r="D34">
         <v>1.574255</v>
@@ -4351,8 +4384,8 @@
         <v>1.8022469999999999</v>
       </c>
       <c r="F34" s="9">
-        <f t="shared" si="0"/>
-        <v>7.0325155209025176</v>
+        <f t="shared" si="1"/>
+        <v>7.0780631067772619</v>
       </c>
       <c r="G34">
         <v>0.83646799999999999</v>
@@ -4361,44 +4394,44 @@
         <v>1.0729630000000001</v>
       </c>
       <c r="I34" s="9">
-        <f t="shared" si="1"/>
-        <v>11.812457652314198</v>
+        <f t="shared" si="2"/>
+        <v>11.888963552331253</v>
       </c>
       <c r="J34">
-        <v>0.91644499999999995</v>
+        <v>0.92524600000000001</v>
       </c>
       <c r="K34">
-        <v>0.32131799999999999</v>
+        <v>0.35407100000000002</v>
       </c>
       <c r="L34">
-        <v>1.505849</v>
+        <v>1.5673630000000001</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" si="2"/>
-        <v>8.4167336831249351</v>
+        <f t="shared" si="3"/>
+        <v>8.1387770414383898</v>
       </c>
       <c r="N34">
-        <v>0.91411299999999995</v>
+        <v>0.96753800000000001</v>
       </c>
       <c r="O34">
-        <v>0.30858099999999999</v>
+        <v>0.32919300000000001</v>
       </c>
       <c r="P34">
-        <v>1.4577560000000001</v>
+        <v>1.5362039999999999</v>
       </c>
       <c r="Q34" s="11">
-        <f t="shared" si="3"/>
-        <v>8.6944111360200189</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="1:19" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>8.3038567794381475</v>
+      </c>
+    </row>
+    <row r="35" spans="1:39" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="1:39" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A37" s="15" t="s">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A37" s="20" t="s">
         <v>11</v>
       </c>
       <c r="B37" s="17" t="s">
@@ -4424,14 +4457,40 @@
       <c r="N37" s="18"/>
       <c r="O37" s="19"/>
       <c r="P37" s="17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q37" s="18"/>
       <c r="R37" s="18"/>
       <c r="S37" s="18"/>
-    </row>
-    <row r="38" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="16"/>
+      <c r="T37" s="18"/>
+      <c r="U37" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="V37" s="18"/>
+      <c r="W37" s="18"/>
+      <c r="X37" s="18"/>
+      <c r="Y37" s="19"/>
+      <c r="Z37" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA37" s="18"/>
+      <c r="AB37" s="18"/>
+      <c r="AC37" s="18"/>
+      <c r="AD37" s="18"/>
+      <c r="AE37" s="18"/>
+      <c r="AF37" s="18"/>
+      <c r="AG37" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH37" s="18"/>
+      <c r="AI37" s="18"/>
+      <c r="AJ37" s="18"/>
+      <c r="AK37" s="18"/>
+      <c r="AL37" s="18"/>
+      <c r="AM37" s="18"/>
+    </row>
+    <row r="38" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="21"/>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
@@ -4475,19 +4534,79 @@
         <v>7</v>
       </c>
       <c r="P38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q38" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Q38" s="6" t="s">
+      <c r="R38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R38" s="6" t="s">
+      <c r="S38" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="S38" s="10" t="s">
+      <c r="T38" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U38" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="V38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="W38" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="X38" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y38" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z38" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD38" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE38" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF38" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG38" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK38" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL38" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM38" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>1</v>
       </c>
@@ -4499,7 +4618,7 @@
       </c>
       <c r="D39" s="13">
         <f>$C$4/C39</f>
-        <v>0.99624072958750776</v>
+        <v>1.0075586558286551</v>
       </c>
       <c r="E39">
         <v>1.7494799999999999</v>
@@ -4509,37 +4628,112 @@
       </c>
       <c r="G39" s="13">
         <f>$C$4/F39</f>
-        <v>0.99575427991104304</v>
+        <v>1.0070666797754877</v>
       </c>
       <c r="H39">
-        <v>2.0046729999999999</v>
+        <v>2.0217879999999999</v>
       </c>
       <c r="I39">
-        <v>2.6870000000000002E-3</v>
+        <v>3.2650000000000001E-3</v>
       </c>
       <c r="J39">
-        <v>2.080848</v>
+        <v>2.1041650000000001</v>
       </c>
       <c r="K39" s="9">
         <f>$C$4/J39</f>
-        <v>0.8712443196235381</v>
+        <v>0.87137795752709502</v>
       </c>
       <c r="L39">
-        <v>2.0056020000000001</v>
+        <v>2.01023</v>
       </c>
       <c r="M39">
-        <v>2.6749999999999999E-3</v>
+        <v>2.526E-3</v>
       </c>
       <c r="N39">
-        <v>2.090541</v>
+        <v>2.0894249999999999</v>
       </c>
       <c r="O39" s="9">
         <f>$C$4/N39</f>
-        <v>0.86720470921163473</v>
-      </c>
-      <c r="S39" s="11"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+        <v>0.87752515644256202</v>
+      </c>
+      <c r="P39">
+        <v>4</v>
+      </c>
+      <c r="Q39">
+        <v>0.50309776299999998</v>
+      </c>
+      <c r="R39">
+        <v>7.5668478999999997E-2</v>
+      </c>
+      <c r="S39">
+        <v>0.64768241900000001</v>
+      </c>
+      <c r="T39" s="9">
+        <f>$C$4/S39</f>
+        <v>2.83089820908046</v>
+      </c>
+      <c r="U39">
+        <v>4</v>
+      </c>
+      <c r="V39">
+        <v>0.51425359800000003</v>
+      </c>
+      <c r="W39">
+        <v>7.5618994999999994E-2</v>
+      </c>
+      <c r="X39">
+        <v>0.660196212</v>
+      </c>
+      <c r="Y39" s="9">
+        <f>$C$4/X39</f>
+        <v>2.777239503458405</v>
+      </c>
+      <c r="Z39">
+        <v>1</v>
+      </c>
+      <c r="AA39">
+        <v>1</v>
+      </c>
+      <c r="AB39">
+        <v>1</v>
+      </c>
+      <c r="AC39">
+        <v>2.0065014589999999</v>
+      </c>
+      <c r="AD39">
+        <v>2.3692940000000001E-3</v>
+      </c>
+      <c r="AE39">
+        <v>2.089318639</v>
+      </c>
+      <c r="AF39" s="9">
+        <f>$C$4/AE39</f>
+        <v>0.87756982863923993</v>
+      </c>
+      <c r="AG39">
+        <v>1</v>
+      </c>
+      <c r="AH39">
+        <v>1</v>
+      </c>
+      <c r="AI39">
+        <v>1</v>
+      </c>
+      <c r="AJ39">
+        <v>2.0402865120000002</v>
+      </c>
+      <c r="AK39">
+        <v>2.458413E-3</v>
+      </c>
+      <c r="AL39">
+        <v>2.1245557530000001</v>
+      </c>
+      <c r="AM39" s="11">
+        <f>$C$4/AL39</f>
+        <v>0.8630147725758458</v>
+      </c>
+    </row>
+    <row r="40" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>2</v>
       </c>
@@ -4551,7 +4745,7 @@
       </c>
       <c r="D40" s="9">
         <f t="shared" ref="D40:D46" si="4">$C$4/C40</f>
-        <v>1.0042525965932696</v>
+        <v>1.0156615427226146</v>
       </c>
       <c r="E40">
         <v>0.87936300000000001</v>
@@ -4561,37 +4755,112 @@
       </c>
       <c r="G40" s="9">
         <f t="shared" ref="G40:G46" si="5">$C$4/F40</f>
-        <v>1.903461331300653</v>
+        <v>1.9250858586972157</v>
       </c>
       <c r="H40">
-        <v>1.004221</v>
+        <v>1.0050319999999999</v>
       </c>
       <c r="I40">
-        <v>3.4972999999999997E-2</v>
+        <v>3.4619999999999998E-2</v>
       </c>
       <c r="J40">
-        <v>1.1179030000000001</v>
+        <v>1.124552</v>
       </c>
       <c r="K40" s="9">
         <f t="shared" ref="K40:K46" si="6">$C$4/J40</f>
-        <v>1.6217212047914711</v>
+        <v>1.6304475026499441</v>
       </c>
       <c r="L40">
-        <v>1.0064690000000001</v>
+        <v>1.016926</v>
       </c>
       <c r="M40">
-        <v>3.8615999999999998E-2</v>
+        <v>4.5919000000000001E-2</v>
       </c>
       <c r="N40">
-        <v>1.1270770000000001</v>
+        <v>1.1453180000000001</v>
       </c>
       <c r="O40" s="9">
         <f t="shared" ref="O40:O46" si="7">$C$4/N40</f>
-        <v>1.6085209794894224</v>
-      </c>
-      <c r="S40" s="11"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+        <v>1.6008855182578112</v>
+      </c>
+      <c r="P40">
+        <v>8</v>
+      </c>
+      <c r="Q40">
+        <v>0.25398512699999998</v>
+      </c>
+      <c r="R40">
+        <v>7.7257800000000001E-2</v>
+      </c>
+      <c r="S40">
+        <v>0.399424538</v>
+      </c>
+      <c r="T40" s="9">
+        <f t="shared" ref="T40:T46" si="8">$C$4/S40</f>
+        <v>4.5904115184831236</v>
+      </c>
+      <c r="U40">
+        <v>8</v>
+      </c>
+      <c r="V40">
+        <v>0.27449818300000001</v>
+      </c>
+      <c r="W40">
+        <v>8.7516162999999994E-2</v>
+      </c>
+      <c r="X40">
+        <v>0.432699157</v>
+      </c>
+      <c r="Y40" s="9">
+        <f t="shared" ref="Y40:Y46" si="9">$C$4/X40</f>
+        <v>4.237408301675984</v>
+      </c>
+      <c r="Z40">
+        <v>1</v>
+      </c>
+      <c r="AA40">
+        <v>2</v>
+      </c>
+      <c r="AB40">
+        <v>2</v>
+      </c>
+      <c r="AC40">
+        <v>1.009906725</v>
+      </c>
+      <c r="AD40">
+        <v>2.9520549999999999E-3</v>
+      </c>
+      <c r="AE40">
+        <v>1.0845280960000001</v>
+      </c>
+      <c r="AF40" s="9">
+        <f t="shared" ref="AF40:AF46" si="10">$C$4/AE40</f>
+        <v>1.6906182576205013</v>
+      </c>
+      <c r="AG40">
+        <v>1</v>
+      </c>
+      <c r="AH40">
+        <v>2</v>
+      </c>
+      <c r="AI40">
+        <v>2</v>
+      </c>
+      <c r="AJ40">
+        <v>1.036417339</v>
+      </c>
+      <c r="AK40">
+        <v>2.2205430000000002E-3</v>
+      </c>
+      <c r="AL40">
+        <v>1.1149560279999999</v>
+      </c>
+      <c r="AM40" s="11">
+        <f t="shared" ref="AM40:AM46" si="11">$C$4/AL40</f>
+        <v>1.6444800996223683</v>
+      </c>
+    </row>
+    <row r="41" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>4</v>
       </c>
@@ -4603,7 +4872,7 @@
       </c>
       <c r="D41" s="9">
         <f t="shared" si="4"/>
-        <v>1.9224611462698722</v>
+        <v>1.9443015236091552</v>
       </c>
       <c r="E41">
         <v>0.44031900000000002</v>
@@ -4613,37 +4882,112 @@
       </c>
       <c r="G41" s="9">
         <f t="shared" si="5"/>
-        <v>3.5476773812272757</v>
-      </c>
-      <c r="H41">
-        <v>0.50616399999999995</v>
-      </c>
-      <c r="I41">
-        <v>8.9519000000000001E-2</v>
-      </c>
-      <c r="J41">
-        <v>0.66897700000000004</v>
-      </c>
-      <c r="K41" s="9">
+        <v>3.5879812452790314</v>
+      </c>
+      <c r="H41" s="15">
+        <v>0.51713900000000002</v>
+      </c>
+      <c r="I41" s="15">
+        <v>7.7720999999999998E-2</v>
+      </c>
+      <c r="J41" s="15">
+        <v>0.67709600000000003</v>
+      </c>
+      <c r="K41" s="16">
         <f t="shared" si="6"/>
-        <v>2.7099989984707991</v>
-      </c>
-      <c r="L41">
-        <v>0.50620100000000001</v>
-      </c>
-      <c r="M41">
-        <v>0.10457900000000001</v>
-      </c>
-      <c r="N41">
-        <v>0.69031699999999996</v>
-      </c>
-      <c r="O41" s="9">
+        <v>2.7079217718019306</v>
+      </c>
+      <c r="L41" s="15">
+        <v>0.507683</v>
+      </c>
+      <c r="M41" s="15">
+        <v>0.100218</v>
+      </c>
+      <c r="N41" s="15">
+        <v>0.68465600000000004</v>
+      </c>
+      <c r="O41" s="16">
         <f t="shared" si="7"/>
-        <v>2.6262238942398928</v>
-      </c>
-      <c r="S41" s="11"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+        <v>2.6780207870813957</v>
+      </c>
+      <c r="P41" s="15">
+        <v>16</v>
+      </c>
+      <c r="Q41" s="15">
+        <v>0.12867648100000001</v>
+      </c>
+      <c r="R41" s="15">
+        <v>7.6324689000000001E-2</v>
+      </c>
+      <c r="S41" s="15">
+        <v>0.273400003</v>
+      </c>
+      <c r="T41" s="16">
+        <f t="shared" si="8"/>
+        <v>6.706375200734727</v>
+      </c>
+      <c r="U41" s="15">
+        <v>16</v>
+      </c>
+      <c r="V41" s="15">
+        <v>0.14175663599999999</v>
+      </c>
+      <c r="W41" s="15">
+        <v>9.8910972E-2</v>
+      </c>
+      <c r="X41" s="15">
+        <v>0.31906516000000001</v>
+      </c>
+      <c r="Y41" s="16">
+        <f t="shared" si="9"/>
+        <v>5.7465471943097768</v>
+      </c>
+      <c r="Z41">
+        <v>2</v>
+      </c>
+      <c r="AA41">
+        <v>2</v>
+      </c>
+      <c r="AB41">
+        <v>4</v>
+      </c>
+      <c r="AC41">
+        <v>0.51271963200000004</v>
+      </c>
+      <c r="AD41">
+        <v>5.3783480000000002E-2</v>
+      </c>
+      <c r="AE41">
+        <v>0.643284203</v>
+      </c>
+      <c r="AF41" s="9">
+        <f t="shared" si="10"/>
+        <v>2.8502534205709384</v>
+      </c>
+      <c r="AG41">
+        <v>2</v>
+      </c>
+      <c r="AH41">
+        <v>2</v>
+      </c>
+      <c r="AI41">
+        <v>4</v>
+      </c>
+      <c r="AJ41">
+        <v>0.59131445100000002</v>
+      </c>
+      <c r="AK41">
+        <v>8.8057294999999994E-2</v>
+      </c>
+      <c r="AL41">
+        <v>0.69871272900000003</v>
+      </c>
+      <c r="AM41" s="11">
+        <f t="shared" si="11"/>
+        <v>2.6241442640155479</v>
+      </c>
+    </row>
+    <row r="42" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>8</v>
       </c>
@@ -4655,7 +4999,7 @@
       </c>
       <c r="D42" s="9">
         <f t="shared" si="4"/>
-        <v>3.5573186979650062</v>
+        <v>3.5977320934868819</v>
       </c>
       <c r="E42">
         <v>0.22437299999999999</v>
@@ -4665,37 +5009,112 @@
       </c>
       <c r="G42" s="9">
         <f t="shared" si="5"/>
-        <v>6.1470780706959394</v>
+        <v>6.2169127744341788</v>
       </c>
       <c r="H42">
-        <v>0.25441999999999998</v>
+        <v>0.25595699999999999</v>
       </c>
       <c r="I42">
-        <v>9.3270000000000006E-2</v>
+        <v>0.118034</v>
       </c>
       <c r="J42">
-        <v>0.42564000000000002</v>
+        <v>0.45441399999999998</v>
       </c>
       <c r="K42" s="9">
         <f t="shared" si="6"/>
-        <v>4.2592965886664782</v>
+        <v>4.0349174981404623</v>
       </c>
       <c r="L42">
-        <v>0.25484099999999998</v>
+        <v>0.28122200000000003</v>
       </c>
       <c r="M42">
-        <v>9.3074000000000004E-2</v>
+        <v>0.13812199999999999</v>
       </c>
       <c r="N42">
-        <v>0.42651899999999998</v>
+        <v>0.47998299999999999</v>
       </c>
       <c r="O42" s="9">
         <f t="shared" si="7"/>
-        <v>4.2505187342181712</v>
-      </c>
-      <c r="S42" s="11"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+        <v>3.8199748741101249</v>
+      </c>
+      <c r="P42">
+        <v>32</v>
+      </c>
+      <c r="Q42">
+        <v>6.6113353999999999E-2</v>
+      </c>
+      <c r="R42">
+        <v>7.3690733999999994E-2</v>
+      </c>
+      <c r="S42">
+        <v>0.210977158</v>
+      </c>
+      <c r="T42" s="9">
+        <f t="shared" si="8"/>
+        <v>8.6906232759093278</v>
+      </c>
+      <c r="U42">
+        <v>32</v>
+      </c>
+      <c r="V42">
+        <v>7.7836308000000007E-2</v>
+      </c>
+      <c r="W42">
+        <v>8.2678809000000006E-2</v>
+      </c>
+      <c r="X42">
+        <v>0.25186906100000001</v>
+      </c>
+      <c r="Y42" s="9">
+        <f t="shared" si="9"/>
+        <v>7.2796674300540625</v>
+      </c>
+      <c r="Z42">
+        <v>2</v>
+      </c>
+      <c r="AA42">
+        <v>4</v>
+      </c>
+      <c r="AB42">
+        <v>8</v>
+      </c>
+      <c r="AC42">
+        <v>0.26235401400000002</v>
+      </c>
+      <c r="AD42">
+        <v>4.5380451000000002E-2</v>
+      </c>
+      <c r="AE42">
+        <v>0.39131629600000001</v>
+      </c>
+      <c r="AF42" s="9">
+        <f t="shared" si="10"/>
+        <v>4.6855268199717397</v>
+      </c>
+      <c r="AG42">
+        <v>2</v>
+      </c>
+      <c r="AH42">
+        <v>4</v>
+      </c>
+      <c r="AI42">
+        <v>8</v>
+      </c>
+      <c r="AJ42">
+        <v>0.30637228500000002</v>
+      </c>
+      <c r="AK42">
+        <v>7.8117846000000005E-2</v>
+      </c>
+      <c r="AL42">
+        <v>0.42161533499999998</v>
+      </c>
+      <c r="AM42" s="11">
+        <f t="shared" si="11"/>
+        <v>4.3488052919137772</v>
+      </c>
+    </row>
+    <row r="43" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>16</v>
       </c>
@@ -4707,7 +5126,7 @@
       </c>
       <c r="D43" s="9">
         <f t="shared" si="4"/>
-        <v>6.2697411422939258</v>
+        <v>6.3409693762860755</v>
       </c>
       <c r="E43">
         <v>0.12690499999999999</v>
@@ -4717,37 +5136,112 @@
       </c>
       <c r="G43" s="9">
         <f t="shared" si="5"/>
-        <v>7.9200665784196795</v>
+        <v>8.010043555567206</v>
       </c>
       <c r="H43">
-        <v>0.13622600000000001</v>
+        <v>0.16810600000000001</v>
       </c>
       <c r="I43">
-        <v>0.105158</v>
+        <v>0.13155</v>
       </c>
       <c r="J43">
-        <v>0.31823299999999999</v>
+        <v>0.340808</v>
       </c>
       <c r="K43" s="9">
         <f t="shared" si="6"/>
-        <v>5.6968541917400142</v>
+        <v>5.3799294617497244</v>
       </c>
       <c r="L43">
-        <v>0.146901</v>
+        <v>0.20425699999999999</v>
       </c>
       <c r="M43">
-        <v>0.13012399999999999</v>
+        <v>0.14940899999999999</v>
       </c>
       <c r="N43">
-        <v>0.33709600000000001</v>
+        <v>0.442602</v>
       </c>
       <c r="O43" s="9">
         <f t="shared" si="7"/>
-        <v>5.3780733084937227</v>
-      </c>
-      <c r="S43" s="11"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+        <v>4.1425998978766474</v>
+      </c>
+      <c r="P43">
+        <v>64</v>
+      </c>
+      <c r="Q43">
+        <v>4.3962521999999997E-2</v>
+      </c>
+      <c r="R43">
+        <v>8.9426810999999995E-2</v>
+      </c>
+      <c r="S43">
+        <v>0.21592866899999999</v>
+      </c>
+      <c r="T43" s="9">
+        <f t="shared" si="8"/>
+        <v>8.491336553368928</v>
+      </c>
+      <c r="U43">
+        <v>64</v>
+      </c>
+      <c r="V43">
+        <v>5.9973138000000002E-2</v>
+      </c>
+      <c r="W43">
+        <v>8.1462149999999997E-2</v>
+      </c>
+      <c r="X43">
+        <v>0.235125732</v>
+      </c>
+      <c r="Y43" s="9">
+        <f t="shared" si="9"/>
+        <v>7.7980533410949677</v>
+      </c>
+      <c r="Z43">
+        <v>4</v>
+      </c>
+      <c r="AA43">
+        <v>4</v>
+      </c>
+      <c r="AB43">
+        <v>16</v>
+      </c>
+      <c r="AC43">
+        <v>0.14599369600000001</v>
+      </c>
+      <c r="AD43">
+        <v>9.1376313000000001E-2</v>
+      </c>
+      <c r="AE43">
+        <v>0.30945852800000001</v>
+      </c>
+      <c r="AF43" s="9">
+        <f t="shared" si="10"/>
+        <v>5.9249393185247747</v>
+      </c>
+      <c r="AG43">
+        <v>4</v>
+      </c>
+      <c r="AH43">
+        <v>4</v>
+      </c>
+      <c r="AI43">
+        <v>16</v>
+      </c>
+      <c r="AJ43">
+        <v>0.15337848000000001</v>
+      </c>
+      <c r="AK43">
+        <v>9.1790815999999997E-2</v>
+      </c>
+      <c r="AL43">
+        <v>0.31635774799999999</v>
+      </c>
+      <c r="AM43" s="11">
+        <f t="shared" si="11"/>
+        <v>5.795726551954087</v>
+      </c>
+    </row>
+    <row r="44" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>32</v>
       </c>
@@ -4759,7 +5253,7 @@
       </c>
       <c r="D44" s="9">
         <f t="shared" si="4"/>
-        <v>9.5638185069713693</v>
+        <v>9.6724695480610468</v>
       </c>
       <c r="E44">
         <v>0.130215</v>
@@ -4769,37 +5263,112 @@
       </c>
       <c r="G44" s="9">
         <f t="shared" si="5"/>
-        <v>8.1634695917650557</v>
+        <v>8.256211781446158</v>
       </c>
       <c r="H44">
-        <v>6.8407999999999997E-2</v>
+        <v>7.3206999999999994E-2</v>
       </c>
       <c r="I44">
-        <v>0.115332</v>
+        <v>0.124931</v>
       </c>
       <c r="J44">
-        <v>0.27040500000000001</v>
+        <v>0.26377600000000001</v>
       </c>
       <c r="K44" s="9">
         <f t="shared" si="6"/>
-        <v>6.7044877128751317</v>
+        <v>6.95106074851389</v>
       </c>
       <c r="L44">
-        <v>9.4672000000000006E-2</v>
+        <v>0.115091</v>
       </c>
       <c r="M44">
-        <v>0.120132</v>
+        <v>0.16541700000000001</v>
       </c>
       <c r="N44">
-        <v>0.27553299999999997</v>
+        <v>0.32397199999999998</v>
       </c>
       <c r="O44" s="9">
         <f t="shared" si="7"/>
-        <v>6.5797091455469952</v>
-      </c>
-      <c r="S44" s="11"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+        <v>5.6595106984554224</v>
+      </c>
+      <c r="P44">
+        <v>128</v>
+      </c>
+      <c r="Q44">
+        <v>4.0862580000000003E-2</v>
+      </c>
+      <c r="R44">
+        <v>7.4088886000000007E-2</v>
+      </c>
+      <c r="S44">
+        <v>0.194909374</v>
+      </c>
+      <c r="T44" s="9">
+        <f t="shared" si="8"/>
+        <v>9.4070539675531464</v>
+      </c>
+      <c r="U44">
+        <v>128</v>
+      </c>
+      <c r="V44">
+        <v>5.7993240000000001E-2</v>
+      </c>
+      <c r="W44">
+        <v>8.4605016000000005E-2</v>
+      </c>
+      <c r="X44">
+        <v>0.23258216800000001</v>
+      </c>
+      <c r="Y44" s="9">
+        <f t="shared" si="9"/>
+        <v>7.8833343749723754</v>
+      </c>
+      <c r="Z44">
+        <v>4</v>
+      </c>
+      <c r="AA44">
+        <v>8</v>
+      </c>
+      <c r="AB44">
+        <v>32</v>
+      </c>
+      <c r="AC44">
+        <v>8.3896393999999999E-2</v>
+      </c>
+      <c r="AD44">
+        <v>9.3016501000000001E-2</v>
+      </c>
+      <c r="AE44">
+        <v>0.255466054</v>
+      </c>
+      <c r="AF44" s="9">
+        <f t="shared" si="10"/>
+        <v>7.1771688304231605</v>
+      </c>
+      <c r="AG44">
+        <v>4</v>
+      </c>
+      <c r="AH44">
+        <v>8</v>
+      </c>
+      <c r="AI44">
+        <v>32</v>
+      </c>
+      <c r="AJ44">
+        <v>9.5941604999999999E-2</v>
+      </c>
+      <c r="AK44">
+        <v>7.5440968999999997E-2</v>
+      </c>
+      <c r="AL44">
+        <v>0.251857689</v>
+      </c>
+      <c r="AM44" s="11">
+        <f t="shared" si="11"/>
+        <v>7.2799961251133372</v>
+      </c>
+    </row>
+    <row r="45" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>64</v>
       </c>
@@ -4811,7 +5380,7 @@
       </c>
       <c r="D45" s="9">
         <f t="shared" si="4"/>
-        <v>8.4869296956192013</v>
+        <v>8.5833465971331471</v>
       </c>
       <c r="E45">
         <v>0.13336100000000001</v>
@@ -4821,37 +5390,112 @@
       </c>
       <c r="G45" s="9">
         <f t="shared" si="5"/>
-        <v>8.4493924861229566</v>
+        <v>8.5453829411408311</v>
       </c>
       <c r="H45">
-        <v>6.2399000000000003E-2</v>
+        <v>6.1040999999999998E-2</v>
       </c>
       <c r="I45">
-        <v>0.124516</v>
+        <v>0.14222099999999999</v>
       </c>
       <c r="J45">
-        <v>0.243452</v>
+        <v>0.25761400000000001</v>
       </c>
       <c r="K45" s="9">
         <f t="shared" si="6"/>
-        <v>7.4467533641128432</v>
+        <v>7.1173266980831782</v>
       </c>
       <c r="L45">
-        <v>7.3104000000000002E-2</v>
+        <v>0.116407</v>
       </c>
       <c r="M45">
-        <v>0.114593</v>
+        <v>0.38983600000000002</v>
       </c>
       <c r="N45">
-        <v>0.25621699999999997</v>
+        <v>0.59950899999999996</v>
       </c>
       <c r="O45" s="9">
         <f t="shared" si="7"/>
-        <v>7.0757482914872947</v>
-      </c>
-      <c r="S45" s="11"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+        <v>3.058374436413799</v>
+      </c>
+      <c r="P45">
+        <v>256</v>
+      </c>
+      <c r="Q45">
+        <v>4.2005105000000001E-2</v>
+      </c>
+      <c r="R45">
+        <v>7.7805784000000003E-2</v>
+      </c>
+      <c r="S45">
+        <v>0.19501533300000001</v>
+      </c>
+      <c r="T45" s="9">
+        <f t="shared" si="8"/>
+        <v>9.4019427692898372</v>
+      </c>
+      <c r="U45">
+        <v>256</v>
+      </c>
+      <c r="V45">
+        <v>7.2628166999999993E-2</v>
+      </c>
+      <c r="W45">
+        <v>7.6768144999999996E-2</v>
+      </c>
+      <c r="X45">
+        <v>0.21139830200000001</v>
+      </c>
+      <c r="Y45" s="9">
+        <f t="shared" si="9"/>
+        <v>8.6733099682134629</v>
+      </c>
+      <c r="Z45">
+        <v>8</v>
+      </c>
+      <c r="AA45">
+        <v>8</v>
+      </c>
+      <c r="AB45">
+        <v>64</v>
+      </c>
+      <c r="AC45">
+        <v>4.6705747999999998E-2</v>
+      </c>
+      <c r="AD45">
+        <v>8.4241409000000003E-2</v>
+      </c>
+      <c r="AE45">
+        <v>0.20239310599999999</v>
+      </c>
+      <c r="AF45" s="9">
+        <f t="shared" si="10"/>
+        <v>9.0592166711449167</v>
+      </c>
+      <c r="AG45">
+        <v>8</v>
+      </c>
+      <c r="AH45">
+        <v>8</v>
+      </c>
+      <c r="AI45">
+        <v>64</v>
+      </c>
+      <c r="AJ45">
+        <v>5.5262914000000003E-2</v>
+      </c>
+      <c r="AK45">
+        <v>8.2436289999999995E-2</v>
+      </c>
+      <c r="AL45">
+        <v>0.224557904</v>
+      </c>
+      <c r="AM45" s="11">
+        <f t="shared" si="11"/>
+        <v>8.1650343512290711</v>
+      </c>
+    </row>
+    <row r="46" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>128</v>
       </c>
@@ -4863,7 +5507,7 @@
       </c>
       <c r="D46" s="9">
         <f t="shared" si="4"/>
-        <v>8.5960635745512128</v>
+        <v>8.6937203061137396</v>
       </c>
       <c r="E46">
         <v>0.13519500000000001</v>
@@ -4873,60 +5517,129 @@
       </c>
       <c r="G46" s="9">
         <f t="shared" si="5"/>
-        <v>8.4809346712511395</v>
+        <v>8.5772834654878025</v>
       </c>
       <c r="H46">
-        <v>3.2120000000000003E-2</v>
+        <v>2.6589000000000002E-2</v>
       </c>
       <c r="I46">
-        <v>0.16891999999999999</v>
+        <v>0.17158999999999999</v>
       </c>
       <c r="J46">
-        <v>0.26001400000000002</v>
+        <v>0.28146300000000002</v>
       </c>
       <c r="K46" s="9">
         <f t="shared" si="6"/>
-        <v>6.9724207158076092</v>
+        <v>6.5142594230858046</v>
       </c>
       <c r="L46">
-        <v>4.6824999999999999E-2</v>
+        <v>3.2827000000000002E-2</v>
       </c>
       <c r="M46">
-        <v>0.17426</v>
+        <v>0.19209899999999999</v>
       </c>
       <c r="N46">
-        <v>0.272845</v>
+        <v>1.1643749999999999</v>
       </c>
       <c r="O46" s="9">
         <f t="shared" si="7"/>
-        <v>6.6445307775476916</v>
-      </c>
-      <c r="S46" s="11"/>
+        <v>1.5746842726784758</v>
+      </c>
+      <c r="P46">
+        <v>512</v>
+      </c>
+      <c r="Q46">
+        <v>4.5719668999999998E-2</v>
+      </c>
+      <c r="R46">
+        <v>7.7309878999999998E-2</v>
+      </c>
+      <c r="S46">
+        <v>0.194904985</v>
+      </c>
+      <c r="T46" s="9">
+        <f t="shared" si="8"/>
+        <v>9.4072658018469877</v>
+      </c>
+      <c r="U46">
+        <v>512</v>
+      </c>
+      <c r="V46">
+        <v>5.7147397000000003E-2</v>
+      </c>
+      <c r="W46">
+        <v>8.4434792999999994E-2</v>
+      </c>
+      <c r="X46">
+        <v>0.22737795</v>
+      </c>
+      <c r="Y46" s="9">
+        <f t="shared" si="9"/>
+        <v>8.0637678367669334</v>
+      </c>
+      <c r="Z46">
+        <v>8</v>
+      </c>
+      <c r="AA46">
+        <v>16</v>
+      </c>
+      <c r="AB46">
+        <v>128</v>
+      </c>
+      <c r="AC46">
+        <v>4.6820715999999998E-2</v>
+      </c>
+      <c r="AD46">
+        <v>0.10161904500000001</v>
+      </c>
+      <c r="AE46">
+        <v>0.20069303599999999</v>
+      </c>
+      <c r="AF46" s="9">
+        <f t="shared" si="10"/>
+        <v>9.1359572636092867</v>
+      </c>
+      <c r="AG46">
+        <v>8</v>
+      </c>
+      <c r="AH46">
+        <v>16</v>
+      </c>
+      <c r="AI46">
+        <v>128</v>
+      </c>
+      <c r="AJ46">
+        <v>6.3690127999999999E-2</v>
+      </c>
+      <c r="AK46">
+        <v>9.7396863E-2</v>
+      </c>
+      <c r="AL46">
+        <v>0.226447019</v>
+      </c>
+      <c r="AM46" s="11">
+        <f t="shared" si="11"/>
+        <v>8.0969182464707128</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="P37:S37"/>
+  <mergeCells count="15">
+    <mergeCell ref="U37:Y37"/>
+    <mergeCell ref="Z37:AF37"/>
+    <mergeCell ref="AG37:AM37"/>
+    <mergeCell ref="P37:T37"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:M2"/>
-    <mergeCell ref="N2:Q2"/>
     <mergeCell ref="A37:A38"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="E37:G37"/>
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="L37:O37"/>
+    <mergeCell ref="N2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE52C848-2688-49C3-8BD1-9A3FE5452517}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Lab 02/graph/RunningTimeRecording.xlsx
+++ b/Lab 02/graph/RunningTimeRecording.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F967F572-3A52-4FCB-B369-3DAD546E02AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AWS" sheetId="2" r:id="rId1"/>
@@ -242,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -290,10 +290,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2569,12 +2565,12 @@
     <col min="2" max="39" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
@@ -2601,12 +2597,11 @@
       <c r="N2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="22"/>
-    </row>
-    <row r="3" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+    </row>
+    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21"/>
       <c r="B3" s="5" t="s">
         <v>5</v>
@@ -2657,7 +2652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>10000000</v>
       </c>
@@ -2714,7 +2709,7 @@
         <v>6.0404658364630697</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>11000000</v>
       </c>
@@ -2771,7 +2766,7 @@
         <v>6.5389482586538739</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>12000000</v>
       </c>
@@ -2828,7 +2823,7 @@
         <v>6.4710100159643096</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>13000000</v>
       </c>
@@ -2885,7 +2880,7 @@
         <v>6.8137534337112999</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>14000000</v>
       </c>
@@ -2942,7 +2937,7 @@
         <v>6.7898613920175155</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>15000000</v>
       </c>
@@ -2999,7 +2994,7 @@
         <v>6.9659841059317005</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>16000000</v>
       </c>
@@ -3056,7 +3051,7 @@
         <v>6.3822040055083873</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>17000000</v>
       </c>
@@ -3113,7 +3108,7 @@
         <v>6.6672262790248116</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>18000000</v>
       </c>
@@ -3170,7 +3165,7 @@
         <v>6.5575099993370598</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>19000000</v>
       </c>
@@ -3227,7 +3222,7 @@
         <v>7.1394078648189367</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>20000000</v>
       </c>
@@ -3284,7 +3279,7 @@
         <v>7.2156871218025032</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>21000000</v>
       </c>
@@ -3341,7 +3336,7 @@
         <v>5.5814066548501629</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>22000000</v>
       </c>

--- a/Lab 02/graph/RunningTimeRecording.xlsx
+++ b/Lab 02/graph/RunningTimeRecording.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\Lab 02\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F967F572-3A52-4FCB-B369-3DAD546E02AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B70B23-2F90-487D-A138-304498E10E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2558,7 +2558,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E341B7-DEDD-4D36-AFDE-6D75EC429377}">
-  <dimension ref="A1:AM46"/>
+  <dimension ref="A1:AM50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" customWidth="1"/>
@@ -5616,6 +5616,12 @@
         <f t="shared" si="11"/>
         <v>8.0969182464707128</v>
       </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="1"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="15">

--- a/Lab 02/graph/RunningTimeRecording.xlsx
+++ b/Lab 02/graph/RunningTimeRecording.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\Lab 02\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B70B23-2F90-487D-A138-304498E10E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F5D9FC-13D6-46B2-A1E5-007807E3E079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AWS" sheetId="2" r:id="rId1"/>
@@ -2683,30 +2683,30 @@
         <v>9.2803245415572118</v>
       </c>
       <c r="J4">
-        <v>0.15099199999999999</v>
+        <v>0.158359</v>
       </c>
       <c r="K4">
-        <v>0.115922</v>
+        <v>0.117295</v>
       </c>
       <c r="L4">
-        <v>0.339115</v>
+        <v>0.32844200000000001</v>
       </c>
       <c r="M4" s="9">
         <f>C4/L4</f>
-        <v>5.4067882576707014</v>
+        <v>5.58248640551452</v>
       </c>
       <c r="N4">
-        <v>0.13047700000000001</v>
+        <v>0.13292200000000001</v>
       </c>
       <c r="O4">
-        <v>0.103162</v>
+        <v>9.4413999999999998E-2</v>
       </c>
       <c r="P4">
-        <v>0.30353999999999998</v>
+        <v>0.299983</v>
       </c>
       <c r="Q4" s="11">
         <f t="shared" ref="Q4:Q34" si="0">C4/P4</f>
-        <v>6.0404658364630697</v>
+        <v>6.1120896850821547</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
@@ -2740,30 +2740,30 @@
         <v>9.6756458328540873</v>
       </c>
       <c r="J5">
-        <v>0.15848000000000001</v>
+        <v>0.15395200000000001</v>
       </c>
       <c r="K5">
-        <v>0.109898</v>
+        <v>0.118075</v>
       </c>
       <c r="L5">
-        <v>0.35133300000000001</v>
+        <v>0.34358899999999998</v>
       </c>
       <c r="M5" s="9">
         <f t="shared" ref="M5:M34" si="3">C5/L5</f>
-        <v>5.9859164951769408</v>
+        <v>6.1208304107523821</v>
       </c>
       <c r="N5">
-        <v>0.164075</v>
+        <v>0.147401</v>
       </c>
       <c r="O5">
-        <v>8.9487999999999998E-2</v>
+        <v>0.10807799999999999</v>
       </c>
       <c r="P5">
-        <v>0.32161899999999999</v>
+        <v>0.33893000000000001</v>
       </c>
       <c r="Q5" s="11">
         <f t="shared" si="0"/>
-        <v>6.5389482586538739</v>
+        <v>6.2049685775823917</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
@@ -2797,30 +2797,30 @@
         <v>9.9394487785624897</v>
       </c>
       <c r="J6">
-        <v>0.19326599999999999</v>
+        <v>0.16897000000000001</v>
       </c>
       <c r="K6">
-        <v>9.5960000000000004E-2</v>
+        <v>0.13872699999999999</v>
       </c>
       <c r="L6">
-        <v>0.38957199999999997</v>
+        <v>0.398783</v>
       </c>
       <c r="M6" s="9">
         <f t="shared" si="3"/>
-        <v>6.0764094955489618</v>
+        <v>5.9360579563321405</v>
       </c>
       <c r="N6">
-        <v>0.17265</v>
+        <v>0.169016</v>
       </c>
       <c r="O6">
-        <v>0.114621</v>
+        <v>0.10080799999999999</v>
       </c>
       <c r="P6">
-        <v>0.36581599999999997</v>
+        <v>0.35795100000000002</v>
       </c>
       <c r="Q6" s="11">
         <f t="shared" si="0"/>
-        <v>6.4710100159643096</v>
+        <v>6.6131928671801443</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
@@ -2854,30 +2854,30 @@
         <v>9.833935717532734</v>
       </c>
       <c r="J7">
-        <v>0.187859</v>
+        <v>0.18779499999999999</v>
       </c>
       <c r="K7">
-        <v>0.13759399999999999</v>
+        <v>0.13355300000000001</v>
       </c>
       <c r="L7">
-        <v>0.442241</v>
+        <v>0.41705100000000001</v>
       </c>
       <c r="M7" s="9">
         <f t="shared" si="3"/>
-        <v>5.967813929509024</v>
+        <v>6.3282716022740626</v>
       </c>
       <c r="N7">
-        <v>0.18529999999999999</v>
+        <v>0.18873999999999999</v>
       </c>
       <c r="O7">
-        <v>0.114091</v>
+        <v>0.11867800000000001</v>
       </c>
       <c r="P7">
-        <v>0.38733600000000001</v>
+        <v>0.40268500000000002</v>
       </c>
       <c r="Q7" s="11">
         <f t="shared" si="0"/>
-        <v>6.8137534337112999</v>
+        <v>6.5540360331276304</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
@@ -2911,30 +2911,30 @@
         <v>10.070341525167184</v>
       </c>
       <c r="J8">
-        <v>0.229714</v>
+        <v>0.226272</v>
       </c>
       <c r="K8">
-        <v>0.13857900000000001</v>
+        <v>0.13220000000000001</v>
       </c>
       <c r="L8">
-        <v>0.46689999999999998</v>
+        <v>0.458727</v>
       </c>
       <c r="M8" s="9">
         <f t="shared" si="3"/>
-        <v>6.2698822017562641</v>
+        <v>6.3815907936528697</v>
       </c>
       <c r="N8">
-        <v>0.22131200000000001</v>
+        <v>0.20989099999999999</v>
       </c>
       <c r="O8">
-        <v>0.11294999999999999</v>
+        <v>0.13617399999999999</v>
       </c>
       <c r="P8">
-        <v>0.43114400000000003</v>
+        <v>0.470775</v>
       </c>
       <c r="Q8" s="11">
         <f t="shared" si="0"/>
-        <v>6.7898613920175155</v>
+        <v>6.2182741224576494</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
@@ -2968,30 +2968,30 @@
         <v>10.409175281652015</v>
       </c>
       <c r="J9">
-        <v>0.23347699999999999</v>
+        <v>0.24607799999999999</v>
       </c>
       <c r="K9">
-        <v>0.15329100000000001</v>
+        <v>0.21884899999999999</v>
       </c>
       <c r="L9">
-        <v>0.56874100000000005</v>
+        <v>0.55828500000000003</v>
       </c>
       <c r="M9" s="9">
         <f t="shared" si="3"/>
-        <v>5.6793725087517863</v>
+        <v>5.785740258111896</v>
       </c>
       <c r="N9">
-        <v>0.22994700000000001</v>
+        <v>0.231767</v>
       </c>
       <c r="O9">
-        <v>0.123031</v>
+        <v>0.15292500000000001</v>
       </c>
       <c r="P9">
-        <v>0.46369500000000002</v>
+        <v>0.48508800000000002</v>
       </c>
       <c r="Q9" s="11">
         <f t="shared" si="0"/>
-        <v>6.9659841059317005</v>
+        <v>6.6587753149943927</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
@@ -3025,30 +3025,30 @@
         <v>10.364619285764599</v>
       </c>
       <c r="J10">
-        <v>0.25047599999999998</v>
+        <v>0.28465299999999999</v>
       </c>
       <c r="K10">
-        <v>0.15142600000000001</v>
+        <v>0.16803499999999999</v>
       </c>
       <c r="L10">
-        <v>0.52703299999999997</v>
+        <v>0.54224300000000003</v>
       </c>
       <c r="M10" s="9">
         <f t="shared" si="3"/>
-        <v>6.7007492889439559</v>
+        <v>6.512792235215576</v>
       </c>
       <c r="N10">
-        <v>0.25673800000000002</v>
+        <v>0.25058799999999998</v>
       </c>
       <c r="O10">
-        <v>0.16491500000000001</v>
+        <v>0.31267099999999998</v>
       </c>
       <c r="P10">
-        <v>0.553338</v>
+        <v>0.67513800000000002</v>
       </c>
       <c r="Q10" s="11">
         <f t="shared" si="0"/>
-        <v>6.3822040055083873</v>
+        <v>5.2308061462989786</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
@@ -3082,30 +3082,30 @@
         <v>10.568362006139441</v>
       </c>
       <c r="J11">
-        <v>0.28723599999999999</v>
+        <v>0.308919</v>
       </c>
       <c r="K11">
-        <v>0.25220500000000001</v>
+        <v>0.28529700000000002</v>
       </c>
       <c r="L11">
-        <v>0.65071800000000002</v>
+        <v>0.71473399999999998</v>
       </c>
       <c r="M11" s="9">
         <f t="shared" si="3"/>
-        <v>5.8832981414376118</v>
+        <v>5.3563535525104449</v>
       </c>
       <c r="N11">
-        <v>0.27944400000000003</v>
+        <v>0.29197000000000001</v>
       </c>
       <c r="O11">
-        <v>0.151396</v>
+        <v>0.16997000000000001</v>
       </c>
       <c r="P11">
-        <v>0.57420700000000002</v>
+        <v>0.57130300000000001</v>
       </c>
       <c r="Q11" s="11">
         <f t="shared" si="0"/>
-        <v>6.6672262790248116</v>
+        <v>6.701116570366338</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
@@ -3139,30 +3139,30 @@
         <v>10.374914155426751</v>
       </c>
       <c r="J12">
-        <v>0.29866700000000002</v>
+        <v>0.31488699999999997</v>
       </c>
       <c r="K12">
-        <v>0.26340999999999998</v>
+        <v>0.16785</v>
       </c>
       <c r="L12">
-        <v>0.69674899999999995</v>
+        <v>0.60999899999999996</v>
       </c>
       <c r="M12" s="9">
         <f t="shared" si="3"/>
-        <v>5.9626321673945712</v>
+        <v>6.8105980501607384</v>
       </c>
       <c r="N12">
-        <v>0.29756899999999997</v>
+        <v>0.30505900000000002</v>
       </c>
       <c r="O12">
-        <v>0.185693</v>
+        <v>0.18024100000000001</v>
       </c>
       <c r="P12">
-        <v>0.63354200000000005</v>
+        <v>0.596696</v>
       </c>
       <c r="Q12" s="11">
         <f t="shared" si="0"/>
-        <v>6.5575099993370598</v>
+        <v>6.9624364835695225</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
@@ -3196,30 +3196,30 @@
         <v>10.743516971128912</v>
       </c>
       <c r="J13">
-        <v>0.33039000000000002</v>
+        <v>0.34288099999999999</v>
       </c>
       <c r="K13">
-        <v>0.16848299999999999</v>
+        <v>0.19398399999999999</v>
       </c>
       <c r="L13">
-        <v>0.626803</v>
+        <v>0.65944700000000001</v>
       </c>
       <c r="M13" s="9">
         <f t="shared" si="3"/>
-        <v>7.1384055277335943</v>
+        <v>6.7850395861987396</v>
       </c>
       <c r="N13">
-        <v>0.32174999999999998</v>
+        <v>0.321216</v>
       </c>
       <c r="O13">
-        <v>0.168183</v>
+        <v>0.22720499999999999</v>
       </c>
       <c r="P13">
-        <v>0.62671500000000002</v>
+        <v>0.679616</v>
       </c>
       <c r="Q13" s="11">
         <f t="shared" si="0"/>
-        <v>7.1394078648189367</v>
+        <v>6.5836796073076558</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
@@ -3253,30 +3253,30 @@
         <v>11.11479447212767</v>
       </c>
       <c r="J14">
-        <v>0.36140699999999998</v>
+        <v>0.38491999999999998</v>
       </c>
       <c r="K14">
-        <v>0.17725199999999999</v>
+        <v>0.18462500000000001</v>
       </c>
       <c r="L14">
-        <v>0.68197700000000006</v>
+        <v>0.78522800000000004</v>
       </c>
       <c r="M14" s="9">
         <f t="shared" si="3"/>
-        <v>7.1007189392017604</v>
+        <v>6.1670330146148622</v>
       </c>
       <c r="N14">
-        <v>0.34512999999999999</v>
+        <v>0.34229399999999999</v>
       </c>
       <c r="O14">
-        <v>0.178616</v>
+        <v>0.17283200000000001</v>
       </c>
       <c r="P14">
-        <v>0.67111100000000001</v>
+        <v>0.67783300000000002</v>
       </c>
       <c r="Q14" s="11">
         <f t="shared" si="0"/>
-        <v>7.2156871218025032</v>
+        <v>7.1441298963018909</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
@@ -3310,30 +3310,30 @@
         <v>11.198254699970891</v>
       </c>
       <c r="J15">
-        <v>0.37110599999999999</v>
+        <v>0.55896299999999999</v>
       </c>
       <c r="K15">
-        <v>0.18732299999999999</v>
+        <v>0.37729299999999999</v>
       </c>
       <c r="L15">
-        <v>0.72574499999999997</v>
+        <v>0.95096599999999998</v>
       </c>
       <c r="M15" s="9">
         <f t="shared" si="3"/>
-        <v>7.1027743904539475</v>
+        <v>5.4205965302650148</v>
       </c>
       <c r="N15">
-        <v>0.37145600000000001</v>
+        <v>0.36841000000000002</v>
       </c>
       <c r="O15">
-        <v>0.40421000000000001</v>
+        <v>0.202318</v>
       </c>
       <c r="P15">
-        <v>0.92356700000000003</v>
+        <v>0.73989000000000005</v>
       </c>
       <c r="Q15" s="11">
         <f t="shared" si="0"/>
-        <v>5.5814066548501629</v>
+        <v>6.9669856329995001</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
@@ -3367,30 +3367,30 @@
         <v>11.203344754346782</v>
       </c>
       <c r="J16">
-        <v>0.39402999999999999</v>
+        <v>0.62112999999999996</v>
       </c>
       <c r="K16">
-        <v>0.22459499999999999</v>
+        <v>0.35870000000000002</v>
       </c>
       <c r="L16">
-        <v>0.79874000000000001</v>
+        <v>0.96110200000000001</v>
       </c>
       <c r="M16" s="9">
         <f t="shared" si="3"/>
-        <v>6.9142649673235352</v>
+        <v>5.7462163225131153</v>
       </c>
       <c r="N16">
-        <v>0.39453300000000002</v>
+        <v>0.39464700000000003</v>
       </c>
       <c r="O16">
-        <v>0.193055</v>
+        <v>0.406003</v>
       </c>
       <c r="P16">
-        <v>0.74716899999999997</v>
+        <v>0.98262700000000003</v>
       </c>
       <c r="Q16" s="11">
         <f t="shared" si="0"/>
-        <v>7.3915004503666513</v>
+        <v>5.6203422051297185</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
@@ -3424,30 +3424,30 @@
         <v>11.115512428552439</v>
       </c>
       <c r="J17">
-        <v>0.44333099999999998</v>
+        <v>0.64727900000000005</v>
       </c>
       <c r="K17">
-        <v>0.180732</v>
+        <v>0.41002</v>
       </c>
       <c r="L17">
-        <v>0.79464500000000005</v>
+        <v>1.1073249999999999</v>
       </c>
       <c r="M17" s="9">
         <f t="shared" si="3"/>
-        <v>7.3662327202713156</v>
+        <v>5.2861987221457118</v>
       </c>
       <c r="N17">
-        <v>0.43036099999999999</v>
+        <v>0.438745</v>
       </c>
       <c r="O17">
-        <v>0.23480100000000001</v>
+        <v>0.40584300000000001</v>
       </c>
       <c r="P17">
-        <v>0.81858600000000004</v>
+        <v>1.009628</v>
       </c>
       <c r="Q17" s="11">
         <f t="shared" si="0"/>
-        <v>7.15079417434454</v>
+        <v>5.7977195561137371</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
@@ -3481,30 +3481,30 @@
         <v>11.149112943864312</v>
       </c>
       <c r="J18">
-        <v>0.47020600000000001</v>
+        <v>0.666601</v>
       </c>
       <c r="K18">
-        <v>0.21249599999999999</v>
+        <v>0.34117500000000001</v>
       </c>
       <c r="L18">
-        <v>0.86087199999999997</v>
+        <v>1.081224</v>
       </c>
       <c r="M18" s="9">
         <f t="shared" si="3"/>
-        <v>7.2218529583956732</v>
+        <v>5.7500490185197517</v>
       </c>
       <c r="N18">
-        <v>0.45207199999999997</v>
+        <v>0.449322</v>
       </c>
       <c r="O18">
-        <v>0.19564100000000001</v>
+        <v>0.20433999999999999</v>
       </c>
       <c r="P18">
-        <v>0.81842599999999999</v>
+        <v>0.82037700000000002</v>
       </c>
       <c r="Q18" s="11">
         <f t="shared" si="0"/>
-        <v>7.5963996744971443</v>
+        <v>7.5783341073677102</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
@@ -3538,30 +3538,30 @@
         <v>11.337223275700525</v>
       </c>
       <c r="J19">
-        <v>0.48530000000000001</v>
+        <v>0.71241100000000002</v>
       </c>
       <c r="K19">
-        <v>0.202236</v>
+        <v>0.37157699999999999</v>
       </c>
       <c r="L19">
-        <v>0.895146</v>
+        <v>1.112711</v>
       </c>
       <c r="M19" s="9">
         <f t="shared" si="3"/>
-        <v>7.3669926470095382</v>
+        <v>5.9265469650250608</v>
       </c>
       <c r="N19">
-        <v>0.478468</v>
+        <v>0.48997000000000002</v>
       </c>
       <c r="O19">
-        <v>0.19278699999999999</v>
+        <v>0.22165799999999999</v>
       </c>
       <c r="P19">
-        <v>0.85243400000000003</v>
+        <v>0.871471</v>
       </c>
       <c r="Q19" s="11">
         <f t="shared" si="0"/>
-        <v>7.7361226792924729</v>
+        <v>7.5671296004112589</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
@@ -3595,30 +3595,30 @@
         <v>11.373074321785525</v>
       </c>
       <c r="J20">
-        <v>0.50156599999999996</v>
+        <v>0.75464699999999996</v>
       </c>
       <c r="K20">
-        <v>0.236147</v>
+        <v>0.397424</v>
       </c>
       <c r="L20">
-        <v>0.93239899999999998</v>
+        <v>1.1497839999999999</v>
       </c>
       <c r="M20" s="9">
         <f t="shared" si="3"/>
-        <v>7.4664483767142604</v>
+        <v>6.0547972488745714</v>
       </c>
       <c r="N20">
-        <v>0.512262</v>
+        <v>0.50050399999999995</v>
       </c>
       <c r="O20">
-        <v>0.24243600000000001</v>
+        <v>0.24956900000000001</v>
       </c>
       <c r="P20">
-        <v>0.92390399999999995</v>
+        <v>0.93007200000000001</v>
       </c>
       <c r="Q20" s="11">
         <f t="shared" si="0"/>
-        <v>7.5350999670961487</v>
+        <v>7.4851291082840898</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
@@ -3652,30 +3652,30 @@
         <v>11.463522343386527</v>
       </c>
       <c r="J21">
-        <v>0.53628699999999996</v>
+        <v>0.80397600000000002</v>
       </c>
       <c r="K21">
-        <v>0.217556</v>
+        <v>0.49065900000000001</v>
       </c>
       <c r="L21">
-        <v>0.920678</v>
+        <v>1.2772380000000001</v>
       </c>
       <c r="M21" s="9">
         <f t="shared" si="3"/>
-        <v>7.953835108474407</v>
+        <v>5.7334036412947311</v>
       </c>
       <c r="N21">
-        <v>0.52862699999999996</v>
+        <v>0.52763599999999999</v>
       </c>
       <c r="O21">
-        <v>0.20550399999999999</v>
+        <v>0.37411100000000003</v>
       </c>
       <c r="P21">
-        <v>0.92293899999999995</v>
+        <v>1.0757680000000001</v>
       </c>
       <c r="Q21" s="11">
         <f t="shared" si="0"/>
-        <v>7.9343499407869862</v>
+        <v>6.8071563757241336</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
@@ -3709,30 +3709,30 @@
         <v>11.38424127818938</v>
       </c>
       <c r="J22">
-        <v>0.56313800000000003</v>
+        <v>0.84965900000000005</v>
       </c>
       <c r="K22">
-        <v>0.21976499999999999</v>
+        <v>0.43257299999999999</v>
       </c>
       <c r="L22">
-        <v>0.96872599999999998</v>
+        <v>1.2294959999999999</v>
       </c>
       <c r="M22" s="9">
         <f t="shared" si="3"/>
-        <v>7.9547116522112553</v>
+        <v>6.267556787496666</v>
       </c>
       <c r="N22">
-        <v>0.56069800000000003</v>
+        <v>0.55309900000000001</v>
       </c>
       <c r="O22">
-        <v>0.25718099999999999</v>
+        <v>0.243867</v>
       </c>
       <c r="P22">
-        <v>0.98792500000000005</v>
+        <v>0.96879800000000005</v>
       </c>
       <c r="Q22" s="11">
         <f t="shared" si="0"/>
-        <v>7.8001224789331172</v>
+        <v>7.9541204668052572</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
@@ -3766,30 +3766,30 @@
         <v>11.491131064656024</v>
       </c>
       <c r="J23">
-        <v>0.58981799999999995</v>
+        <v>0.81898599999999999</v>
       </c>
       <c r="K23">
-        <v>0.25647399999999998</v>
+        <v>0.440635</v>
       </c>
       <c r="L23">
-        <v>1.0602940000000001</v>
+        <v>1.275082</v>
       </c>
       <c r="M23" s="9">
         <f t="shared" si="3"/>
-        <v>7.6245597919067727</v>
+        <v>6.3402000812496757</v>
       </c>
       <c r="N23">
-        <v>0.580515</v>
+        <v>0.58268799999999998</v>
       </c>
       <c r="O23">
-        <v>0.25049399999999999</v>
+        <v>0.48466700000000001</v>
       </c>
       <c r="P23">
-        <v>1.045582</v>
+        <v>1.252869</v>
       </c>
       <c r="Q23" s="11">
         <f t="shared" si="0"/>
-        <v>7.7318421701980329</v>
+        <v>6.4526099695977788</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
@@ -3823,30 +3823,30 @@
         <v>11.640461580076922</v>
       </c>
       <c r="J24">
-        <v>0.627085</v>
+        <v>0.91010199999999997</v>
       </c>
       <c r="K24">
-        <v>0.22342300000000001</v>
+        <v>0.52471599999999996</v>
       </c>
       <c r="L24">
-        <v>1.115772</v>
+        <v>1.341078</v>
       </c>
       <c r="M24" s="9">
         <f t="shared" si="3"/>
-        <v>7.5979026180976046</v>
+        <v>6.321427239877174</v>
       </c>
       <c r="N24">
-        <v>0.62524800000000003</v>
+        <v>0.92688599999999999</v>
       </c>
       <c r="O24">
-        <v>0.29843799999999998</v>
+        <v>0.416628</v>
       </c>
       <c r="P24">
-        <v>1.152817</v>
+        <v>1.335647</v>
       </c>
       <c r="Q24" s="11">
         <f t="shared" si="0"/>
-        <v>7.3537491206323296</v>
+        <v>6.3471313902550603</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
@@ -3880,30 +3880,30 @@
         <v>11.724953598923941</v>
       </c>
       <c r="J25">
-        <v>0.66337100000000004</v>
+        <v>0.96265000000000001</v>
       </c>
       <c r="K25">
-        <v>0.271125</v>
+        <v>0.55198499999999995</v>
       </c>
       <c r="L25">
-        <v>1.1492789999999999</v>
+        <v>1.423224</v>
       </c>
       <c r="M25" s="9">
         <f t="shared" si="3"/>
-        <v>7.7667581153053344</v>
+        <v>6.2717969904948196</v>
       </c>
       <c r="N25">
-        <v>0.644459</v>
+        <v>1.013549</v>
       </c>
       <c r="O25">
-        <v>0.233075</v>
+        <v>0.54068000000000005</v>
       </c>
       <c r="P25">
-        <v>1.112115</v>
+        <v>1.3936759999999999</v>
       </c>
       <c r="Q25" s="11">
         <f t="shared" si="0"/>
-        <v>8.0263030352076896</v>
+        <v>6.4047683966718232</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
@@ -3937,30 +3937,30 @@
         <v>11.548214773771958</v>
       </c>
       <c r="J26">
-        <v>0.672543</v>
+        <v>1.1409929999999999</v>
       </c>
       <c r="K26">
-        <v>0.26406600000000002</v>
+        <v>0.537852</v>
       </c>
       <c r="L26">
-        <v>1.202148</v>
+        <v>1.5018290000000001</v>
       </c>
       <c r="M26" s="9">
         <f t="shared" si="3"/>
-        <v>7.7325088092314749</v>
+        <v>6.1895328962218725</v>
       </c>
       <c r="N26">
-        <v>0.67047699999999999</v>
+        <v>0.90211300000000005</v>
       </c>
       <c r="O26">
-        <v>0.258687</v>
+        <v>0.35764400000000002</v>
       </c>
       <c r="P26">
-        <v>1.1586460000000001</v>
+        <v>1.2257</v>
       </c>
       <c r="Q26" s="11">
         <f t="shared" si="0"/>
-        <v>8.0228300965091996</v>
+        <v>7.583927551603165</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
@@ -3994,30 +3994,30 @@
         <v>11.717468787428851</v>
       </c>
       <c r="J27">
-        <v>0.72667400000000004</v>
+        <v>1.0330630000000001</v>
       </c>
       <c r="K27">
-        <v>0.296962</v>
+        <v>0.43043199999999998</v>
       </c>
       <c r="L27">
-        <v>1.2120230000000001</v>
+        <v>1.5568519999999999</v>
       </c>
       <c r="M27" s="9">
         <f t="shared" si="3"/>
-        <v>8.0152249586022695</v>
+        <v>6.2399232553897228</v>
       </c>
       <c r="N27">
-        <v>0.71296899999999996</v>
+        <v>0.95007699999999995</v>
       </c>
       <c r="O27">
-        <v>0.28098499999999998</v>
+        <v>0.37767699999999998</v>
       </c>
       <c r="P27">
-        <v>1.2481009999999999</v>
+        <v>1.29935</v>
       </c>
       <c r="Q27" s="11">
         <f t="shared" si="0"/>
-        <v>7.7835343453774977</v>
+        <v>7.4765359602878361</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
@@ -4051,30 +4051,30 @@
         <v>11.59327012737654</v>
       </c>
       <c r="J28">
-        <v>0.74124800000000002</v>
+        <v>1.056972</v>
       </c>
       <c r="K28">
-        <v>0.30798300000000001</v>
+        <v>0.67115999999999998</v>
       </c>
       <c r="L28">
-        <v>1.343232</v>
+        <v>1.7181850000000001</v>
       </c>
       <c r="M28" s="9">
         <f t="shared" si="3"/>
-        <v>7.5158021845816663</v>
+        <v>5.8756571614814463</v>
       </c>
       <c r="N28">
-        <v>0.75077300000000002</v>
+        <v>0.75881900000000002</v>
       </c>
       <c r="O28">
-        <v>0.26050499999999999</v>
+        <v>0.31161499999999998</v>
       </c>
       <c r="P28">
-        <v>1.2219789999999999</v>
+        <v>1.269665</v>
       </c>
       <c r="Q28" s="11">
         <f t="shared" si="0"/>
-        <v>8.2615707798579194</v>
+        <v>7.9512832125009352</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
@@ -4108,30 +4108,30 @@
         <v>11.787094695318363</v>
       </c>
       <c r="J29">
-        <v>0.759544</v>
+        <v>1.057499</v>
       </c>
       <c r="K29">
-        <v>0.26486599999999999</v>
+        <v>0.56684900000000005</v>
       </c>
       <c r="L29">
-        <v>1.2783770000000001</v>
+        <v>1.6322589999999999</v>
       </c>
       <c r="M29" s="9">
         <f t="shared" si="3"/>
-        <v>8.2696199947276892</v>
+        <v>6.4767245884384774</v>
       </c>
       <c r="N29">
-        <v>0.76310999999999996</v>
+        <v>1.008057</v>
       </c>
       <c r="O29">
-        <v>0.29046699999999998</v>
+        <v>0.51230299999999995</v>
       </c>
       <c r="P29">
-        <v>1.2952410000000001</v>
+        <v>1.497668</v>
       </c>
       <c r="Q29" s="11">
         <f t="shared" si="0"/>
-        <v>8.1619497838626174</v>
+        <v>7.0587686990708223</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
@@ -4165,30 +4165,30 @@
         <v>11.876873996049751</v>
       </c>
       <c r="J30">
-        <v>0.79788199999999998</v>
+        <v>1.309056</v>
       </c>
       <c r="K30">
-        <v>0.29107899999999998</v>
+        <v>0.65164100000000003</v>
       </c>
       <c r="L30">
-        <v>1.3376049999999999</v>
+        <v>1.796872</v>
       </c>
       <c r="M30" s="9">
         <f t="shared" si="3"/>
-        <v>8.3301983769498467</v>
+        <v>6.2010621791646816</v>
       </c>
       <c r="N30">
-        <v>0.80297399999999997</v>
+        <v>1.15601</v>
       </c>
       <c r="O30">
-        <v>0.29154999999999998</v>
+        <v>0.63595400000000002</v>
       </c>
       <c r="P30">
-        <v>1.32508</v>
+        <v>1.6548480000000001</v>
       </c>
       <c r="Q30" s="11">
         <f t="shared" si="0"/>
-        <v>8.408937573580463</v>
+        <v>6.7332558639826736</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
@@ -4222,30 +4222,30 @@
         <v>11.501824052437341</v>
       </c>
       <c r="J31">
-        <v>0.82260699999999998</v>
+        <v>1.275881</v>
       </c>
       <c r="K31">
-        <v>0.31930199999999997</v>
+        <v>0.68803499999999995</v>
       </c>
       <c r="L31">
-        <v>1.3924650000000001</v>
+        <v>1.9653590000000001</v>
       </c>
       <c r="M31" s="9">
         <f t="shared" si="3"/>
-        <v>8.1760324316948711</v>
+        <v>5.7927528761920843</v>
       </c>
       <c r="N31">
-        <v>0.82231699999999996</v>
+        <v>1.1226119999999999</v>
       </c>
       <c r="O31">
-        <v>0.32889400000000002</v>
+        <v>0.550122</v>
       </c>
       <c r="P31">
-        <v>1.4191320000000001</v>
+        <v>1.62758</v>
       </c>
       <c r="Q31" s="11">
         <f t="shared" si="0"/>
-        <v>8.0223960843670632</v>
+        <v>6.9949489426018996</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
@@ -4279,30 +4279,30 @@
         <v>11.766438843260019</v>
       </c>
       <c r="J32">
-        <v>0.85871200000000003</v>
+        <v>1.346724</v>
       </c>
       <c r="K32">
-        <v>0.37237700000000001</v>
+        <v>0.71832700000000005</v>
       </c>
       <c r="L32">
-        <v>1.488686</v>
+        <v>2.0130629999999998</v>
       </c>
       <c r="M32" s="9">
         <f t="shared" si="3"/>
-        <v>7.9354773269850067</v>
+        <v>5.8683876262193495</v>
       </c>
       <c r="N32">
-        <v>0.853016</v>
+        <v>1.0741860000000001</v>
       </c>
       <c r="O32">
-        <v>0.361595</v>
+        <v>0.50409400000000004</v>
       </c>
       <c r="P32">
-        <v>1.48349</v>
+        <v>1.5886480000000001</v>
       </c>
       <c r="Q32" s="11">
         <f t="shared" si="0"/>
-        <v>7.963271744332622</v>
+        <v>7.436155775225223</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.35">
@@ -4336,30 +4336,30 @@
         <v>11.814064826678672</v>
       </c>
       <c r="J33">
-        <v>0.96537600000000001</v>
+        <v>1.015223</v>
       </c>
       <c r="K33">
-        <v>0.29770099999999999</v>
+        <v>0.32330100000000001</v>
       </c>
       <c r="L33">
-        <v>1.5088649999999999</v>
+        <v>1.556818</v>
       </c>
       <c r="M33" s="9">
         <f t="shared" si="3"/>
-        <v>8.1396089113340171</v>
+        <v>7.8888932424984803</v>
       </c>
       <c r="N33">
-        <v>0.92100199999999999</v>
+        <v>1.3149360000000001</v>
       </c>
       <c r="O33">
-        <v>0.27014500000000002</v>
+        <v>0.75881399999999999</v>
       </c>
       <c r="P33">
-        <v>1.585299</v>
+        <v>1.8738220000000001</v>
       </c>
       <c r="Q33" s="11">
         <f t="shared" si="0"/>
-        <v>7.7471637842451164</v>
+        <v>6.5542890413283645</v>
       </c>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.35">
@@ -4393,30 +4393,30 @@
         <v>11.888963552331253</v>
       </c>
       <c r="J34">
-        <v>0.92524600000000001</v>
+        <v>0.92412700000000003</v>
       </c>
       <c r="K34">
-        <v>0.35407100000000002</v>
+        <v>0.34673700000000002</v>
       </c>
       <c r="L34">
-        <v>1.5673630000000001</v>
+        <v>1.526659</v>
       </c>
       <c r="M34" s="9">
         <f t="shared" si="3"/>
-        <v>8.1387770414383898</v>
+        <v>8.3557742757223448</v>
       </c>
       <c r="N34">
-        <v>0.96753800000000001</v>
+        <v>1.0146500000000001</v>
       </c>
       <c r="O34">
-        <v>0.32919300000000001</v>
+        <v>0.39776</v>
       </c>
       <c r="P34">
-        <v>1.5362039999999999</v>
+        <v>1.5783240000000001</v>
       </c>
       <c r="Q34" s="11">
         <f t="shared" si="0"/>
-        <v>8.3038567794381475</v>
+        <v>8.082255607847312</v>
       </c>
     </row>
     <row r="35" spans="1:39" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4626,62 +4626,62 @@
         <v>1.0070666797754877</v>
       </c>
       <c r="H39">
-        <v>2.0217879999999999</v>
+        <v>2.0125489999999999</v>
       </c>
       <c r="I39">
-        <v>3.2650000000000001E-3</v>
+        <v>2.545E-3</v>
       </c>
       <c r="J39">
-        <v>2.1041650000000001</v>
+        <v>2.0870690000000001</v>
       </c>
       <c r="K39" s="9">
         <f>$C$4/J39</f>
-        <v>0.87137795752709502</v>
+        <v>0.87851575582790986</v>
       </c>
       <c r="L39">
-        <v>2.01023</v>
+        <v>2.0076520000000002</v>
       </c>
       <c r="M39">
-        <v>2.526E-3</v>
+        <v>2.3809999999999999E-3</v>
       </c>
       <c r="N39">
-        <v>2.0894249999999999</v>
+        <v>2.0981580000000002</v>
       </c>
       <c r="O39" s="9">
         <f>$C$4/N39</f>
-        <v>0.87752515644256202</v>
+        <v>0.87387270167451636</v>
       </c>
       <c r="P39">
         <v>4</v>
       </c>
       <c r="Q39">
-        <v>0.50309776299999998</v>
+        <v>0.50400231600000001</v>
       </c>
       <c r="R39">
-        <v>7.5668478999999997E-2</v>
+        <v>8.1135895999999999E-2</v>
       </c>
       <c r="S39">
-        <v>0.64768241900000001</v>
+        <v>0.65400648699999997</v>
       </c>
       <c r="T39" s="9">
         <f>$C$4/S39</f>
-        <v>2.83089820908046</v>
+        <v>2.8035241797227006</v>
       </c>
       <c r="U39">
         <v>4</v>
       </c>
       <c r="V39">
-        <v>0.51425359800000003</v>
+        <v>0.52087092599999996</v>
       </c>
       <c r="W39">
-        <v>7.5618994999999994E-2</v>
+        <v>8.3368353000000006E-2</v>
       </c>
       <c r="X39">
-        <v>0.660196212</v>
+        <v>0.67356958</v>
       </c>
       <c r="Y39" s="9">
         <f>$C$4/X39</f>
-        <v>2.777239503458405</v>
+        <v>2.7220988810094422</v>
       </c>
       <c r="Z39">
         <v>1</v>
@@ -4693,17 +4693,17 @@
         <v>1</v>
       </c>
       <c r="AC39">
-        <v>2.0065014589999999</v>
+        <v>2.0094351160000001</v>
       </c>
       <c r="AD39">
-        <v>2.3692940000000001E-3</v>
+        <v>2.579212E-3</v>
       </c>
       <c r="AE39">
-        <v>2.089318639</v>
+        <v>2.0819791639999998</v>
       </c>
       <c r="AF39" s="9">
         <f>$C$4/AE39</f>
-        <v>0.87756982863923993</v>
+        <v>0.8806634723842991</v>
       </c>
       <c r="AG39">
         <v>1</v>
@@ -4753,62 +4753,62 @@
         <v>1.9250858586972157</v>
       </c>
       <c r="H40">
-        <v>1.0050319999999999</v>
+        <v>1.007638</v>
       </c>
       <c r="I40">
-        <v>3.4619999999999998E-2</v>
+        <v>4.3213000000000001E-2</v>
       </c>
       <c r="J40">
-        <v>1.124552</v>
+        <v>1.1195759999999999</v>
       </c>
       <c r="K40" s="9">
         <f t="shared" ref="K40:K46" si="6">$C$4/J40</f>
-        <v>1.6304475026499441</v>
+        <v>1.6376940913345768</v>
       </c>
       <c r="L40">
-        <v>1.016926</v>
+        <v>1.006578</v>
       </c>
       <c r="M40">
-        <v>4.5919000000000001E-2</v>
+        <v>3.4758999999999998E-2</v>
       </c>
       <c r="N40">
-        <v>1.1453180000000001</v>
+        <v>1.1131850000000001</v>
       </c>
       <c r="O40" s="9">
         <f t="shared" ref="O40:O46" si="7">$C$4/N40</f>
-        <v>1.6008855182578112</v>
+        <v>1.6470963945795172</v>
       </c>
       <c r="P40">
         <v>8</v>
       </c>
       <c r="Q40">
-        <v>0.25398512699999998</v>
+        <v>0.25935507899999999</v>
       </c>
       <c r="R40">
-        <v>7.7257800000000001E-2</v>
+        <v>8.2989639000000004E-2</v>
       </c>
       <c r="S40">
-        <v>0.399424538</v>
+        <v>0.41128780799999998</v>
       </c>
       <c r="T40" s="9">
         <f t="shared" ref="T40:T46" si="8">$C$4/S40</f>
-        <v>4.5904115184831236</v>
+        <v>4.458004745912624</v>
       </c>
       <c r="U40">
         <v>8</v>
       </c>
       <c r="V40">
-        <v>0.27449818300000001</v>
+        <v>0.27571733999999998</v>
       </c>
       <c r="W40">
-        <v>8.7516162999999994E-2</v>
+        <v>7.9636594000000005E-2</v>
       </c>
       <c r="X40">
-        <v>0.432699157</v>
+        <v>0.43212537899999998</v>
       </c>
       <c r="Y40" s="9">
         <f t="shared" ref="Y40:Y46" si="9">$C$4/X40</f>
-        <v>4.237408301675984</v>
+        <v>4.243034751263707</v>
       </c>
       <c r="Z40">
         <v>1</v>
@@ -4820,17 +4820,17 @@
         <v>2</v>
       </c>
       <c r="AC40">
-        <v>1.009906725</v>
+        <v>1.02567016</v>
       </c>
       <c r="AD40">
-        <v>2.9520549999999999E-3</v>
+        <v>2.9438910000000001E-3</v>
       </c>
       <c r="AE40">
-        <v>1.0845280960000001</v>
+        <v>1.0956829180000001</v>
       </c>
       <c r="AF40" s="9">
         <f t="shared" ref="AF40:AF46" si="10">$C$4/AE40</f>
-        <v>1.6906182576205013</v>
+        <v>1.6734065758247039</v>
       </c>
       <c r="AG40">
         <v>1</v>
@@ -4880,62 +4880,62 @@
         <v>3.5879812452790314</v>
       </c>
       <c r="H41" s="15">
-        <v>0.51713900000000002</v>
+        <v>0.50651999999999997</v>
       </c>
       <c r="I41" s="15">
-        <v>7.7720999999999998E-2</v>
+        <v>7.7217999999999995E-2</v>
       </c>
       <c r="J41" s="15">
-        <v>0.67709600000000003</v>
+        <v>0.65427400000000002</v>
       </c>
       <c r="K41" s="16">
         <f t="shared" si="6"/>
-        <v>2.7079217718019306</v>
+        <v>2.8023779028358149</v>
       </c>
       <c r="L41" s="15">
-        <v>0.507683</v>
+        <v>0.51406799999999997</v>
       </c>
       <c r="M41" s="15">
-        <v>0.100218</v>
+        <v>9.1689999999999994E-2</v>
       </c>
       <c r="N41" s="15">
-        <v>0.68465600000000004</v>
+        <v>0.66680899999999999</v>
       </c>
       <c r="O41" s="16">
         <f t="shared" si="7"/>
-        <v>2.6780207870813957</v>
+        <v>2.749697439596646</v>
       </c>
       <c r="P41" s="15">
         <v>16</v>
       </c>
       <c r="Q41" s="15">
-        <v>0.12867648100000001</v>
+        <v>0.12997271599999999</v>
       </c>
       <c r="R41" s="15">
-        <v>7.6324689000000001E-2</v>
+        <v>7.9282255999999995E-2</v>
       </c>
       <c r="S41" s="15">
-        <v>0.273400003</v>
+        <v>0.28451030999999999</v>
       </c>
       <c r="T41" s="16">
         <f t="shared" si="8"/>
-        <v>6.706375200734727</v>
+        <v>6.4444870205230878</v>
       </c>
       <c r="U41" s="15">
         <v>16</v>
       </c>
       <c r="V41" s="15">
-        <v>0.14175663599999999</v>
+        <v>0.142735691</v>
       </c>
       <c r="W41" s="15">
-        <v>9.8910972E-2</v>
+        <v>9.2170550000000004E-2</v>
       </c>
       <c r="X41" s="15">
-        <v>0.31906516000000001</v>
+        <v>0.31031044299999999</v>
       </c>
       <c r="Y41" s="16">
         <f t="shared" si="9"/>
-        <v>5.7465471943097768</v>
+        <v>5.9086732056903415</v>
       </c>
       <c r="Z41">
         <v>2</v>
@@ -4947,17 +4947,17 @@
         <v>4</v>
       </c>
       <c r="AC41">
-        <v>0.51271963200000004</v>
+        <v>0.51376098400000003</v>
       </c>
       <c r="AD41">
-        <v>5.3783480000000002E-2</v>
+        <v>3.6810080000000002E-2</v>
       </c>
       <c r="AE41">
-        <v>0.643284203</v>
+        <v>0.61898913300000002</v>
       </c>
       <c r="AF41" s="9">
         <f t="shared" si="10"/>
-        <v>2.8502534205709384</v>
+        <v>2.9621247001762789</v>
       </c>
       <c r="AG41">
         <v>2</v>
@@ -5007,62 +5007,62 @@
         <v>6.2169127744341788</v>
       </c>
       <c r="H42">
-        <v>0.25595699999999999</v>
+        <v>0.25619700000000001</v>
       </c>
       <c r="I42">
-        <v>0.118034</v>
+        <v>0.118398</v>
       </c>
       <c r="J42">
-        <v>0.45441399999999998</v>
+        <v>0.45153100000000002</v>
       </c>
       <c r="K42" s="9">
         <f t="shared" si="6"/>
-        <v>4.0349174981404623</v>
+        <v>4.0606802190768736</v>
       </c>
       <c r="L42">
-        <v>0.28122200000000003</v>
+        <v>0.25673099999999999</v>
       </c>
       <c r="M42">
-        <v>0.13812199999999999</v>
+        <v>9.6532999999999994E-2</v>
       </c>
       <c r="N42">
-        <v>0.47998299999999999</v>
+        <v>0.42132900000000001</v>
       </c>
       <c r="O42" s="9">
         <f t="shared" si="7"/>
-        <v>3.8199748741101249</v>
+        <v>4.3517607380455656</v>
       </c>
       <c r="P42">
         <v>32</v>
       </c>
       <c r="Q42">
-        <v>6.6113353999999999E-2</v>
+        <v>6.7847225999999997E-2</v>
       </c>
       <c r="R42">
-        <v>7.3690733999999994E-2</v>
+        <v>8.8775026000000007E-2</v>
       </c>
       <c r="S42">
-        <v>0.210977158</v>
+        <v>0.24454773399999999</v>
       </c>
       <c r="T42" s="9">
         <f t="shared" si="8"/>
-        <v>8.6906232759093278</v>
+        <v>7.4976078085434237</v>
       </c>
       <c r="U42">
         <v>32</v>
       </c>
       <c r="V42">
-        <v>7.7836308000000007E-2</v>
+        <v>8.5379263999999996E-2</v>
       </c>
       <c r="W42">
-        <v>8.2678809000000006E-2</v>
+        <v>7.4831569000000001E-2</v>
       </c>
       <c r="X42">
-        <v>0.25186906100000001</v>
+        <v>0.22587592500000001</v>
       </c>
       <c r="Y42" s="9">
         <f t="shared" si="9"/>
-        <v>7.2796674300540625</v>
+        <v>8.1173901114074027</v>
       </c>
       <c r="Z42">
         <v>2</v>
@@ -5074,17 +5074,17 @@
         <v>8</v>
       </c>
       <c r="AC42">
-        <v>0.26235401400000002</v>
+        <v>0.257368282</v>
       </c>
       <c r="AD42">
-        <v>4.5380451000000002E-2</v>
+        <v>3.8216607E-2</v>
       </c>
       <c r="AE42">
-        <v>0.39131629600000001</v>
+        <v>0.36613054099999998</v>
       </c>
       <c r="AF42" s="9">
         <f t="shared" si="10"/>
-        <v>4.6855268199717397</v>
+        <v>5.0078395399415756</v>
       </c>
       <c r="AG42">
         <v>2</v>
@@ -5134,62 +5134,62 @@
         <v>8.010043555567206</v>
       </c>
       <c r="H43">
-        <v>0.16810600000000001</v>
+        <v>0.13081999999999999</v>
       </c>
       <c r="I43">
-        <v>0.13155</v>
+        <v>0.114271</v>
       </c>
       <c r="J43">
-        <v>0.340808</v>
+        <v>0.31677699999999998</v>
       </c>
       <c r="K43" s="9">
         <f t="shared" si="6"/>
-        <v>5.3799294617497244</v>
+        <v>5.788055951031799</v>
       </c>
       <c r="L43">
-        <v>0.20425699999999999</v>
+        <v>0.134629</v>
       </c>
       <c r="M43">
-        <v>0.14940899999999999</v>
+        <v>0.117523</v>
       </c>
       <c r="N43">
-        <v>0.442602</v>
+        <v>0.33444600000000002</v>
       </c>
       <c r="O43" s="9">
         <f t="shared" si="7"/>
-        <v>4.1425998978766474</v>
+        <v>5.4822691854589376</v>
       </c>
       <c r="P43">
         <v>64</v>
       </c>
       <c r="Q43">
-        <v>4.3962521999999997E-2</v>
+        <v>4.5449837999999999E-2</v>
       </c>
       <c r="R43">
-        <v>8.9426810999999995E-2</v>
+        <v>8.1442596000000006E-2</v>
       </c>
       <c r="S43">
-        <v>0.21592866899999999</v>
+        <v>0.208405286</v>
       </c>
       <c r="T43" s="9">
         <f t="shared" si="8"/>
-        <v>8.491336553368928</v>
+        <v>8.797871854363617</v>
       </c>
       <c r="U43">
         <v>64</v>
       </c>
       <c r="V43">
-        <v>5.9973138000000002E-2</v>
+        <v>6.4181950000000001E-2</v>
       </c>
       <c r="W43">
-        <v>8.1462149999999997E-2</v>
+        <v>7.9622618000000006E-2</v>
       </c>
       <c r="X43">
-        <v>0.235125732</v>
+        <v>0.206069323</v>
       </c>
       <c r="Y43" s="9">
         <f t="shared" si="9"/>
-        <v>7.7980533410949677</v>
+        <v>8.89760287124348</v>
       </c>
       <c r="Z43">
         <v>4</v>
@@ -5201,17 +5201,17 @@
         <v>16</v>
       </c>
       <c r="AC43">
-        <v>0.14599369600000001</v>
+        <v>0.13562723500000001</v>
       </c>
       <c r="AD43">
-        <v>9.1376313000000001E-2</v>
+        <v>9.1811561E-2</v>
       </c>
       <c r="AE43">
-        <v>0.30945852800000001</v>
+        <v>0.28866418500000002</v>
       </c>
       <c r="AF43" s="9">
         <f t="shared" si="10"/>
-        <v>5.9249393185247747</v>
+        <v>6.3517509108377954</v>
       </c>
       <c r="AG43">
         <v>4</v>
@@ -5261,62 +5261,62 @@
         <v>8.256211781446158</v>
       </c>
       <c r="H44">
-        <v>7.3206999999999994E-2</v>
+        <v>7.0437E-2</v>
       </c>
       <c r="I44">
-        <v>0.124931</v>
+        <v>0.13061800000000001</v>
       </c>
       <c r="J44">
-        <v>0.26377600000000001</v>
+        <v>0.275285</v>
       </c>
       <c r="K44" s="9">
         <f t="shared" si="6"/>
-        <v>6.95106074851389</v>
+        <v>6.6604537116079703</v>
       </c>
       <c r="L44">
-        <v>0.115091</v>
+        <v>8.4344000000000002E-2</v>
       </c>
       <c r="M44">
-        <v>0.16541700000000001</v>
+        <v>0.14436099999999999</v>
       </c>
       <c r="N44">
-        <v>0.32397199999999998</v>
+        <v>0.291711</v>
       </c>
       <c r="O44" s="9">
         <f t="shared" si="7"/>
-        <v>5.6595106984554224</v>
+        <v>6.2854091892318085</v>
       </c>
       <c r="P44">
         <v>128</v>
       </c>
       <c r="Q44">
-        <v>4.0862580000000003E-2</v>
+        <v>4.0907881E-2</v>
       </c>
       <c r="R44">
-        <v>7.4088886000000007E-2</v>
+        <v>7.7078984000000003E-2</v>
       </c>
       <c r="S44">
-        <v>0.194909374</v>
+        <v>0.197255654</v>
       </c>
       <c r="T44" s="9">
         <f t="shared" si="8"/>
-        <v>9.4070539675531464</v>
+        <v>9.295160685229332</v>
       </c>
       <c r="U44">
         <v>128</v>
       </c>
       <c r="V44">
-        <v>5.7993240000000001E-2</v>
+        <v>5.4632679000000003E-2</v>
       </c>
       <c r="W44">
-        <v>8.4605016000000005E-2</v>
+        <v>8.0054173000000006E-2</v>
       </c>
       <c r="X44">
-        <v>0.23258216800000001</v>
+        <v>0.20088941799999999</v>
       </c>
       <c r="Y44" s="9">
         <f t="shared" si="9"/>
-        <v>7.8833343749723754</v>
+        <v>9.1270262926442456</v>
       </c>
       <c r="Z44">
         <v>4</v>
@@ -5328,17 +5328,17 @@
         <v>32</v>
       </c>
       <c r="AC44">
-        <v>8.3896393999999999E-2</v>
+        <v>9.0762625999999999E-2</v>
       </c>
       <c r="AD44">
-        <v>9.3016501000000001E-2</v>
+        <v>0.10557999999999999</v>
       </c>
       <c r="AE44">
-        <v>0.255466054</v>
+        <v>0.23804515200000001</v>
       </c>
       <c r="AF44" s="9">
         <f t="shared" si="10"/>
-        <v>7.1771688304231605</v>
+        <v>7.7024168927414243</v>
       </c>
       <c r="AG44">
         <v>4</v>
@@ -5388,62 +5388,62 @@
         <v>8.5453829411408311</v>
       </c>
       <c r="H45">
-        <v>6.1040999999999998E-2</v>
+        <v>5.4615999999999998E-2</v>
       </c>
       <c r="I45">
-        <v>0.14222099999999999</v>
+        <v>0.14677200000000001</v>
       </c>
       <c r="J45">
-        <v>0.25761400000000001</v>
+        <v>0.31840499999999999</v>
       </c>
       <c r="K45" s="9">
         <f t="shared" si="6"/>
-        <v>7.1173266980831782</v>
+        <v>5.7584617075736881</v>
       </c>
       <c r="L45">
-        <v>0.116407</v>
+        <v>8.9492000000000002E-2</v>
       </c>
       <c r="M45">
-        <v>0.38983600000000002</v>
+        <v>0.38211099999999998</v>
       </c>
       <c r="N45">
-        <v>0.59950899999999996</v>
+        <v>0.58205700000000005</v>
       </c>
       <c r="O45" s="9">
         <f t="shared" si="7"/>
-        <v>3.058374436413799</v>
+        <v>3.1500746490463989</v>
       </c>
       <c r="P45">
         <v>256</v>
       </c>
       <c r="Q45">
-        <v>4.2005105000000001E-2</v>
+        <v>4.3968985000000002E-2</v>
       </c>
       <c r="R45">
-        <v>7.7805784000000003E-2</v>
+        <v>7.3524079000000006E-2</v>
       </c>
       <c r="S45">
-        <v>0.19501533300000001</v>
+        <v>0.19201752</v>
       </c>
       <c r="T45" s="9">
         <f t="shared" si="8"/>
-        <v>9.4019427692898372</v>
+        <v>9.548727636936464</v>
       </c>
       <c r="U45">
         <v>256</v>
       </c>
       <c r="V45">
-        <v>7.2628166999999993E-2</v>
+        <v>5.8024407E-2</v>
       </c>
       <c r="W45">
-        <v>7.6768144999999996E-2</v>
+        <v>7.6971701000000003E-2</v>
       </c>
       <c r="X45">
-        <v>0.21139830200000001</v>
+        <v>0.20095970099999999</v>
       </c>
       <c r="Y45" s="9">
         <f t="shared" si="9"/>
-        <v>8.6733099682134629</v>
+        <v>9.1238342358003415</v>
       </c>
       <c r="Z45">
         <v>8</v>
@@ -5455,17 +5455,17 @@
         <v>64</v>
       </c>
       <c r="AC45">
-        <v>4.6705747999999998E-2</v>
+        <v>4.2871419000000001E-2</v>
       </c>
       <c r="AD45">
-        <v>8.4241409000000003E-2</v>
+        <v>9.9493572000000002E-2</v>
       </c>
       <c r="AE45">
-        <v>0.20239310599999999</v>
+        <v>0.201019964</v>
       </c>
       <c r="AF45" s="9">
         <f t="shared" si="10"/>
-        <v>9.0592166711449167</v>
+        <v>9.1210990367106035</v>
       </c>
       <c r="AG45">
         <v>8</v>
@@ -5515,62 +5515,62 @@
         <v>8.5772834654878025</v>
       </c>
       <c r="H46">
-        <v>2.6589000000000002E-2</v>
+        <v>3.4470000000000001E-2</v>
       </c>
       <c r="I46">
-        <v>0.17158999999999999</v>
+        <v>0.21360399999999999</v>
       </c>
       <c r="J46">
-        <v>0.28146300000000002</v>
+        <v>0.32069399999999998</v>
       </c>
       <c r="K46" s="9">
         <f t="shared" si="6"/>
-        <v>6.5142594230858046</v>
+        <v>5.7173598508235273</v>
       </c>
       <c r="L46">
-        <v>3.2827000000000002E-2</v>
+        <v>9.1230000000000006E-2</v>
       </c>
       <c r="M46">
-        <v>0.19209899999999999</v>
+        <v>0.26694299999999999</v>
       </c>
       <c r="N46">
-        <v>1.1643749999999999</v>
+        <v>1.1234329999999999</v>
       </c>
       <c r="O46" s="9">
         <f t="shared" si="7"/>
-        <v>1.5746842726784758</v>
+        <v>1.6320715165034321</v>
       </c>
       <c r="P46">
         <v>512</v>
       </c>
       <c r="Q46">
-        <v>4.5719668999999998E-2</v>
+        <v>4.9633458999999998E-2</v>
       </c>
       <c r="R46">
-        <v>7.7309878999999998E-2</v>
+        <v>8.7728959999999995E-2</v>
       </c>
       <c r="S46">
-        <v>0.194904985</v>
+        <v>0.218067396</v>
       </c>
       <c r="T46" s="9">
         <f t="shared" si="8"/>
-        <v>9.4072658018469877</v>
+        <v>8.4080565624766752</v>
       </c>
       <c r="U46">
         <v>512</v>
       </c>
       <c r="V46">
-        <v>5.7147397000000003E-2</v>
+        <v>5.9965857999999997E-2</v>
       </c>
       <c r="W46">
-        <v>8.4434792999999994E-2</v>
+        <v>8.0049586000000006E-2</v>
       </c>
       <c r="X46">
-        <v>0.22737795</v>
+        <v>0.207548657</v>
       </c>
       <c r="Y46" s="9">
         <f t="shared" si="9"/>
-        <v>8.0637678367669334</v>
+        <v>8.834183880072036</v>
       </c>
       <c r="Z46">
         <v>8</v>
@@ -5582,17 +5582,17 @@
         <v>128</v>
       </c>
       <c r="AC46">
-        <v>4.6820715999999998E-2</v>
+        <v>3.5805198000000003E-2</v>
       </c>
       <c r="AD46">
-        <v>0.10161904500000001</v>
+        <v>0.138961533</v>
       </c>
       <c r="AE46">
-        <v>0.20069303599999999</v>
+        <v>0.23217156799999999</v>
       </c>
       <c r="AF46" s="9">
         <f t="shared" si="10"/>
-        <v>9.1359572636092867</v>
+        <v>7.8972762073950422</v>
       </c>
       <c r="AG46">
         <v>8</v>
